--- a/linkedin_fixed_14APR2026.xlsx
+++ b/linkedin_fixed_14APR2026.xlsx
@@ -582,12 +582,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1,408,835</t>
+          <t>1,408,843</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-nbd_investment-opportunities-activity-7449456364818538496-6BUf?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAs6OSMBXTCKUygorc4R5fEL3sZA8ddDMKA</t>
+          <t>https://www.linkedin.com/posts/emirates-nbd_investment-opportunities-activity-7449456364818538496-6BUf?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFaCCHUBO31VBTHSBm179qVphLOHl1clqxM</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Access equities, sukuk, bonds, and precious metals on ENBD X. • Invest in gold and silver through a single platform. • Start investing today on ENBD X.</t>
+          <t>access equities, sukuk, bonds and precious metals (gold and silver), all on enbd x. • start investing today on enbd x</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -694,12 +694,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1,408,835</t>
+          <t>1,408,843</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-nbd_investment-advisory-solutions-activity-7449426164294524928-ZSVJ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAs6OSMBXTCKUygorc4R5fEL3sZA8ddDMKA</t>
+          <t>https://www.linkedin.com/posts/emirates-nbd_investment-advisory-solutions-activity-7449426164294524928-ZSVJ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFaCCHUBO31VBTHSBm179qVphLOHl1clqxM</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Expert advisors create tailored investment strategies for clients. • Strategies align with individual goals and risk profiles. • Focus on identifying promising investment trends.</t>
+          <t>#emiratesnbd #privatebanking #investmentadvisory #investwithconfidence</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1,408,835</t>
+          <t>1,408,843</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-nbd_fight-fraud-stay-vigilant-against-scammers-activity-7449406609786822656-ZlVp?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAs6OSMBXTCKUygorc4R5fEL3sZA8ddDMKA</t>
+          <t>https://www.linkedin.com/posts/emirates-nbd_fight-fraud-stay-vigilant-against-scammers-activity-7449406609786822656-ZlVp?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFaCCHUBO31VBTHSBm179qVphLOHl1clqxM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Avoid urgency tactics used by scammers. • Scammers pressure you to act quickly. • Stay safe and vigilant against fraud.</t>
+          <t>stay safe, stay vigilant. • scammers rush you to act fast.</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1,408,835</t>
+          <t>1,408,843</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-nbd_proud-to-have-hamad-zayed-group-head-of-activity-7449364567257686016-msS8?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAs6OSMBXTCKUygorc4R5fEL3sZA8ddDMKA</t>
+          <t>https://www.linkedin.com/posts/emirates-nbd_proud-to-have-hamad-zayed-group-head-of-activity-7449364567257686016-msS8?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFaCCHUBO31VBTHSBm179qVphLOHl1clqxM</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Hamad Zayed graduated from the Nafis leadership program. • Ceremony attended by Sheikh Mansoor and Sheikh Abdullah bin Zayed. • Highlights commitment to UAE's vision for empowered national talent.</t>
+          <t>this milestone reflects his leadership, dedication, and commitment to supporting the uae’s vision for empowered national talent. • congratulations, hamad a proud moment for all of us. • يعكس هذا الإنجاز قيادته والتزامه بدعم رؤية دولة الإمارات في تمكين الكفاءات الوطنية.</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1004,13 +1004,1062 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Banky Egypt</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46125.92028388889</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>📌يعزز #Apple_Pay 📲 تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر
+للتفاصيل👈 https://lnkd.in/dDFennux
+#بنكي
+‏Emirates NBD</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>219,366</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/banky-egypt_appleabrpay-aeqaeuaerabraepaesaenaetaepaezaepaesabraexaeqaeyabraepaesaewaefaeuaey-activity-7449518067010760705-YEmT?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449518067010760705</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>يعزز #apple_pay تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر للتفاصيل  #بنكي ‏emirates nbd</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Banky Egypt</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>يعزز #apple_pay تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر للتفاصيل  #بنكي ‏emirates nbd</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>يعزز #apple_pay تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر للتفاصيل #بنكي ‏emirates nbd</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mohammad Nadeem</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46125.91631365741</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Grateful to receive this appreciation for my contribution to our DX Engineering Practices.
+This journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. It took a lot of deep dives, iterations, and persistence, but absolutely worth it.
+A big thank you to my manager, leadership, and the entire team for the support and trust throughout.
+Looking forward to building more and pushing boundaries! 
+Emirates NBD  Miguel Rio-Tinto  Ahmad Kayyali Speridian UAE  Speridian Technologies 
+#Gratitude #TeamWork #Engineering #ContinuousLearning</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ndm-0501_gratitude-teamwork-engineering-activity-7449516628246949888-X0hs?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449516628246949888</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>grateful to receive this appreciation for my contribution to our dx engineering practices. this journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. it took a lot of deep dives, iterations, and persistence, but absolutely worth it. a big thank you to my manager, leadership, and the entire team for the support and trust throughout. looking forward to building more and pushing boundaries! emirates nbd miguel rio-tinto ahmad kayyali speridian uae speridian technologies #gratitude #teamwork #engineering #continuouslearning</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mohammad Nadeem</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>grateful to receive this appreciation for my contribution to our dx engineering practices. this journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. it took a lot of deep dives, iterations, and persistence, but absolutely worth it. a big thank you to my manager, leadership, and the entire team for the support and trust throughout. looking forward to building more and pushing boundaries! emirates nbd miguel rio-tinto ahmad kayyali speridian uae speridian technologies #gratitude #teamwork #engineering #continuouslearning</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>emirates nbd miguel rio-tinto ahmad kayyali speridian uae speridian technologies #gratitude #teamwork #engineering #continuouslearning • this journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. • a big thank you to my manager, leadership, and the entire team for the support and trust throughout.</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Marketics Agency</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46125.90151929398</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quelle banque recommandez-vous ?
+Prenez le temps de répondre honnêtement.
+Notre analyse du secteur bancaire marocain — et de ce que JPMorgan, Emirates NBD et Bank of America ont compris avant tout le monde — est disponible en document joint.
+Marketics | Agence Marketing &amp; Communication</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/marketics-premiumagency_secteur-bancaire-toutes-les-banques-sont-activity-7449511266949156864-ntuA?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449511266949156864</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>quelle banque recommandez-vous ? prenez le temps de répondre honnêtement. notre analyse du secteur bancaire marocain — et de ce que jpmorgan, emirates nbd et bank of america ont compris avant tout le monde — est disponible en document joint. marketics | agence marketing &amp; communication</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Marketics Agency</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>quelle banque recommandez-vous ? prenez le temps de répondre honnêtement. notre analyse du secteur bancaire marocain — et de ce que jpmorgan, emirates nbd et bank of america ont compris avant tout le monde — est disponible en document joint. marketics | agence marketing &amp; communication</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>notre analyse du secteur bancaire marocain — et de ce que jpmorgan, emirates nbd et bank of america ont compris avant tout le monde — est disponible en document joint. • prenez le temps de répondre honnêtement. • quelle banque recommandez-vous ?</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aswila Sood</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>46125.8570941088</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>I am pleased to have completed the One Million Prompters program, initiative by the Dubai Future Foundation and the Dubai Centre for Artificial Intelligence.
+I extend my sincere gratitude to His Highness Sheikh Hamdan bin Mohammed bin Rashid Al Maktoum for this opportunity, and to Emirates NBD for their support.
+This certification has strengthened my skills in generative AI and prompt engineering, preparing me for an AI-driven future.
+#OneMillionPrompters #AI #GenerativeAI #FutureSkills #Dubai
+#LearningAndDevelopment#EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/aswila-sood-0758539b_onemillionprompters-ai-generativeai-activity-7449495167801389056-jXWi?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449495167801389056</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>i am pleased to have completed the one million prompters program, initiative by the dubai future foundation and the dubai centre for artificial intelligence. i extend my sincere gratitude to his highness sheikh hamdan bin mohammed bin rashid al maktoum for this opportunity, and to emirates nbd for their support. this certification has strengthened my skills in generative ai and prompt engineering, preparing me for an ai-driven future. #onemillionprompters #ai #generativeai #futureskills #dubai #learninganddevelopment#emiratesnbd</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Aswila Sood</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>i am pleased to have completed the one million prompters program, initiative by the dubai future foundation and the dubai centre for artificial intelligence. i extend my sincere gratitude to his highness sheikh hamdan bin mohammed bin rashid al maktoum for this opportunity, and to emirates nbd for their support. this certification has strengthened my skills in generative ai and prompt engineering, preparing me for an ai-driven future. #onemillionprompters #ai #generativeai #futureskills #dubai #learninganddevelopment#emiratesnbd</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>i am pleased to have completed the one million prompters program, initiative by the dubai future foundation and the dubai centre for artificial intelligence. • i extend my sincere gratitude to his highness sheikh hamdan bin mohammed bin rashid al maktoum for this opportunity, and to emirates nbd for their support. • this certification has strengthened my skills in generative ai and prompt engineering, preparing me for an ai-driven future.</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brunella Lupano</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>46125.84993825232</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>As of April 2026, the #UAE's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. This total is heavily anchored by the International Holding Company LLC (#IHC), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value. 
+Top 10 #UAE Companies by Market Capitalization (2026)
+Based on the Forbes Middle East 2026 ranking, the most valuable publicly listed companies in the UAE are:
+International Holding Company LLC (IHC): $238.6 billion
+TAQA Group (Abu Dhabi National Energy Company): $87.9 billion
+ADNOC Group: $75.4 billion
+First Abu Dhabi Bank (FAB): $56.0 billion
+Emirates NBD Group: $53.5 billion
+e&amp; UAE (formerly etisalat Group): $46.7 billion
+Dubai Electricity &amp; Water Authority - DEWA: $41.1 billion
+Emaar Dubai Properties: $36.1 billion
+Abu Dhabi Commercial Bank (ADCB)
+Alpha Dhabi Holding (ADH) 
+Market Composition and Key #Trends
+&gt; Sector Dominance: The #Banking and #Financial #Services sector remains the most represented, featuring major players like FAB, Emirates NBD, and ADCB.
+&gt; Regional Context: The UAE leads the region in the number of companies on the "Top 100 Most Valuable" list with 35 entries, slightly ahead of Saudi Arabia's 34.
+&gt; #Energy and Utility Weight: Despite having fewer companies than the financial sector, the #Energy sector (including TAQA and ADNOC Gas) commands immense #market #value due to the scale of hydrocarbon and utility operations.
+&gt; Exchange #Resilience: Market gains in early 2026 were supported by a 6.4% rise in the Dubai Financial Market (DFM) and a 2.9% gain in the Abu Dhabi Securities Exchange (ADX) during January.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/brunellalupano_uae-valuable-companies-activity-7449492574605680640-hR0W?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449492574605680640</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>as of april 2026, the #uae's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. this total is heavily anchored by the international holding company llc (#ihc), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value. top 10 #uae companies by market capitalization (2026) based on the forbes middle east 2026 ranking, the most valuable publicly listed companies in the uae are: international holding company llc (ihc): $238.6 billion taqa group (abu dhabi national energy company): $87.9 billion adnoc group: $75.4 billion first abu dhabi bank (fab): $56.0 billion emirates nbd group: $53.5 billion e&amp; uae (formerly etisalat group): $46.7 billion dubai electricity &amp; water authority - dewa: $41.1 billion emaar dubai properties: $36.1 billion abu dhabi commercial bank (adcb) alpha dhabi holding (adh) market composition and key #trends &gt; sector dominance: the #banking and #financial #services sector remains the most represented, featuring major players like fab, emirates nbd, and adcb. &gt; regional context: the uae leads the region in the number of companies on the "top 100 most valuable" list with 35 entries, slightly ahead of saudi arabia's 34. &gt; #energy and utility weight: despite having fewer companies than the financial sector, the #energy sector (including taqa and adnoc gas) commands immense #market #value due to the scale of hydrocarbon and utility operations. &gt; exchange #resilience: market gains in early 2026 were supported by a 6.4% rise in the dubai financial market (dfm) and a 2.9% gain in the abu dhabi securities exchange (adx) during january.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Brunella Lupano</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>as of april 2026, the #uae's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. this total is heavily anchored by the international holding company llc (#ihc), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value. top 10 #uae companies by market capitalization (2026) based on the forbes middle east 2026 ranking, the most valuable publicly listed companies in the uae are: international holding company llc (ihc): $238.6 billion taqa group (abu dhabi national energy company): $87.9 billion adnoc group: $75.4 billion first abu dhabi bank (fab): $56.0 billion emirates nbd group: $53.5 billion e&amp; uae (formerly etisalat group): $46.7 billion dubai electricity &amp; water authority - dewa: $41.1 billion emaar dubai properties: $36.1 billion abu dhabi commercial bank (adcb) alpha dhabi holding (adh) market composition and key #trends &gt; sector dominance: the #banking and #financial #services sector remains the most represented, featuring major players like fab, emirates nbd, and adcb. &gt; regional context: the uae leads the region in the number of companies on the "top 100 most valuable" list with 35 entries, slightly ahead of saudi arabia's 34. &gt; #energy and utility weight: despite having fewer companies than the financial sector, the #energy sector (including taqa and adnoc gas) commands immense #market #value due to the scale of hydrocarbon and utility operations. &gt; exchange #resilience: market gains in early 2026 were supported by a 6.4% rise in the dubai financial market (dfm) and a 2.9% gain in the abu dhabi securities exchange (adx) during january.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>&gt; exchange #resilience: market gains in early 2026 were supported by a 6.4% rise in the dubai financial market (dfm) and a 2.9% gain in the abu dhabi securities exchange (adx) during january. • as of april 2026, the #uae's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. • this total is heavily anchored by the international holding company llc (#ihc), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PakBanker</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>46125.77408923611</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Central Bank of The UAE has confirmed that its 1 trillion dirham Financial Institutions Resilience Package successfully insulated the economy from regional shocks. Governor Khaled Mohamed Balama and major bank CEOs reported robust growth, with total assets reaching 5.5 trillion dirhams alongside significant progress in digital projects like the Jaywan card scheme and Aani payments. Read more: https://lnkd.in/ddNF9Qvb
+Mustafa Al Khalfawi | National Bank of Umm Al Qaiwain (P.S.C), is Licensed by the Central Bank of the UAE | Emirates NBD | First Abu Dhabi Bank (FAB) | Abu Dhabi Islamic Bank - Egypt | Ajman Bank | Dubai Islamic Bank Pakistan | Mashreq | Abu Dhabi Commercial Bank
+#pakbanker #pakistanbankingnews #banksinpakistan #PAKBANKER #PakBanker #CBUAE #UAEBanking #FinancialResilience #DigitalFinance #Jaywan #AaniPayments #KhaledBalama #Fintech #GlobalFinance #BankingStability #DigitalTransformation #SMEsupport #EconomyUAE #FinancialInfrastructure #SecurityCompliance</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2,153</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/pakbanker_central-bank-of-the-uae-reports-success-in-activity-7449465087842758656-dQqv?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449465087842758656</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>the central bank of the uae has confirmed that its 1 trillion dirham financial institutions resilience package successfully insulated the economy from regional shocks. governor khaled mohamed balama and major bank ceos reported robust growth, with total assets reaching 5.5 trillion dirhams alongside significant progress in digital projects like the jaywan card scheme and aani payments. read more:  mustafa al khalfawi | national bank of umm al qaiwain (p.s.c), is licensed by the central bank of the uae | emirates nbd | first abu dhabi bank (fab) | abu dhabi islamic bank - egypt | ajman bank | dubai islamic bank pakistan | mashreq | abu dhabi commercial bank #pakbanker #pakistanbankingnews #banksinpakistan #pakbanker #pakbanker #cbuae #uaebanking #financialresilience #digitalfinance #jaywan #aanipayments #khaledbalama #fintech #globalfinance #bankingstability #digitaltransformation #smesupport #economyuae #financialinfrastructure #securitycompliance</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PakBanker</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>the central bank of the uae has confirmed that its 1 trillion dirham financial institutions resilience package successfully insulated the economy from regional shocks. governor khaled mohamed balama and major bank ceos reported robust growth, with total assets reaching 5.5 trillion dirhams alongside significant progress in digital projects like the jaywan card scheme and aani payments. read more:  mustafa al khalfawi | national bank of umm al qaiwain (p.s.c), is licensed by the central bank of the uae | emirates nbd | first abu dhabi bank (fab) | abu dhabi islamic bank - egypt | ajman bank | dubai islamic bank pakistan | mashreq | abu dhabi commercial bank #pakbanker #pakistanbankingnews #banksinpakistan #pakbanker #pakbanker #cbuae #uaebanking #financialresilience #digitalfinance #jaywan #aanipayments #khaledbalama #fintech #globalfinance #bankingstability #digitaltransformation #smesupport #economyuae #financialinfrastructure #securitycompliance</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>the central bank of the uae has confirmed that its 1 trillion dirham financial institutions resilience package successfully insulated the economy from regional shocks.</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Climena Middle East</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>46125.75018515046</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Title:
+Where ESG Intelligence Meets Shariah-Compliant Digital Finance
+Speakers:
+Fahad Siddiqui - CEO &amp; Founder, Al Mabrook Finance
+Sajjeed Aslam - Partner, Sustainadility LLC USA
+Hina Nasir - Partner, Sustainadility LLC USA
+In this snippet, Fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with Real World Asset (RWA) tokens that are backed by tangible, physical assets.
+He explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas RWA tokens are anchored in real assets such as real estate, commodities, or infrastructure. 
+This fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets.
+Full Session : https://lnkd.in/dWEZyPaX
+Climena Middle East SAJJEED ASLAM Faraz Khan MBE Hina Nasir Kashif (Kash) Aqeel Ahsan Abdullah Khan Fahad Siddiqui Emirates NBD First Abu Dhabi Bank (FAB) Abu Dhabi Commercial Bank Dubai Islamic Bank Pakistan Mashreq Corporate &amp; Investment Banking Group RAKBANK Commercial Bank of Dubai Abu Dhabi Islamic Bank - Egypt Sharjah Islamic Bank Ajman Bank National Bank of Fujairah (NBF) Bank of Sharjah Commercial Bank HSBC Standard Chartered National Bank of Bahrain The Saudi National Bank - SNB</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>linkedinVideo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/climena-middle-east_title-where-esg-intelligence-meets-shariah-compliant-activity-7449456425292005377-B0hY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449456425292005377</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Climena Middle East</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>11</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets.</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sustainadility</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>46125.75000565972</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Title:
+Where ESG Intelligence Meets Shariah-Compliant Digital Finance
+Speakers:
+Fahad Siddiqui - CEO &amp; Founder, Al Mabrook Finance
+Sajjeed Aslam - Partner, Sustainadility LLC USA 
+Hina Nasir - Partner, Sustainadility LLC USA
+In this snippet, Fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with Real World Asset (RWA) tokens that are backed by tangible, physical assets.
+He explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas RWA tokens are anchored in real assets such as real estate, commodities, or infrastructure. 
+This fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets.
+Full Session : https://lnkd.in/dWEZyPaX
+Climena Middle East SAJJEED ASLAM Faraz Khan MBE Hina Nasir Kashif (Kash) Aqeel Ahsan Abdullah Khan Fahad Siddiqui Emirates NBD First Abu Dhabi Bank (FAB) Abu Dhabi Commercial Bank Dubai Islamic Bank Pakistan Mashreq Corporate &amp; Investment Banking Group RAKBANK Commercial Bank of Dubai Abu Dhabi Islamic Bank - Egypt Sharjah Islamic Bank Ajman Bank National Bank of Fujairah (NBF) Bank of Sharjah Commercial Bank HSBC Standard Chartered National Bank of Bahrain The Saudi National Bank - SNB</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>linkedinVideo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1,486</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sustainadility_title-where-esg-intelligence-meets-shariah-compliant-activity-7449456360246722560-R-3z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449456360246722560</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sustainadility</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>12</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets.</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AliveNow - Creative Tech Studio</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46125.73963571759</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stop Interacting. Start Co-Creating: Why TikTok Branded Effects are the Ultimate ROI Driver for 2026. 🚀
+The marketing funnel has changed. It’s no longer about getting a user to watch your ad; it’s about getting them to participate in it. If your brand is on TikTok, Branded Effects are the bridge between passive scrolling and active brand advocacy. At AliveNow, we’ve seen first-hand how immersive AR experiences transform digital campaigns into cultural moments.
+Why are Branded Effects a game-changer for Brand Managers?
+✅ Unrivaled UGC Engine: Unlike traditional ads, AR effects invite users to create content for you. This results in authentic, high-volume User Generated Content that builds trust and virality.
+✅ Low Friction, High Engagement: No third-party apps. These effects live natively in the TikTok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3D portals.
+✅ Gamification &amp; Rewards: From decibel-based challenges to AR sports games, we build experiences that drive real-world actions—like unlocking coupons or entering giveaways.
+✅ Measurable Impact: It’s not just "vibes." We track total impressions, effect uses, shares, and engagement data to ensure your campaign delivers a tangible ROI.
+Our Track Record with Branded TikTok AR effects: 
+We’ve been busy helping global leaders redefine their TikTok presence. Some of our recent work includes:
+Nestlé: A vocal-chord-powered challenge to unlock virtual rewards.
+McDonald’s: A delicious AR game catching McCrispy burgers.
+Emirates NBD: Celebrating partnerships with immersive gesture-based games.
+Colgate, Aldi, and Hellman’s: From 3D face morphing to interactive food pairings.
+The Best Part?
+Whether it’s a simple 3-day build or a complex 3D world-tracking experience, our team at AliveNow handles the entire lifecycle—from concept and design to TikTok platform approval.
+Ready to turn your audience into your biggest content creators? Let’s build something viral.
+👉 Explore our TikTok AR Gallery: https://lnkd.in/gWgcjuEd
+#TikTokMarketing #AugmentedReality #BrandedEffects #TikTokAR #TikTokBrandedEffects #DigitalMarketing #BrandStrategy #UGC #AliveNow #CreativeTech #MarketingInnovation #ARforBusiness</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6,262</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/alivenow_tiktok-ar-branded-effects-for-marketing-campaigns-activity-7449452602305536000-UqHv?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449452602305536000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>stop interacting. start co-creating: why tiktok branded effects are the ultimate roi driver for 2026. the marketing funnel has changed. it’s no longer about getting a user to watch your ad; it’s about getting them to participate in it. if your brand is on tiktok, branded effects are the bridge between passive scrolling and active brand advocacy. at alivenow, we’ve seen first-hand how immersive ar experiences transform digital campaigns into cultural moments. why are branded effects a game-changer for brand managers? unrivaled ugc engine: unlike traditional ads, ar effects invite users to create content for you. this results in authentic, high-volume user generated content that builds trust and virality. low friction, high engagement: no third-party apps. these effects live natively in the tiktok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3d portals. gamification &amp; rewards: from decibel-based challenges to ar sports games, we build experiences that drive real-world actions—like unlocking coupons or entering giveaways. measurable impact: it’s not just "vibes." we track total impressions, effect uses, shares, and engagement data to ensure your campaign delivers a tangible roi. our track record with branded tiktok ar effects: we’ve been busy helping global leaders redefine their tiktok presence. some of our recent work includes: nestlé: a vocal-chord-powered challenge to unlock virtual rewards. mcdonald’s: a delicious ar game catching mccrispy burgers. emirates nbd: celebrating partnerships with immersive gesture-based games. colgate, aldi, and hellman’s: from 3d face morphing to interactive food pairings. the best part? whether it’s a simple 3-day build or a complex 3d world-tracking experience, our team at alivenow handles the entire lifecycle—from concept and design to tiktok platform approval. ready to turn your audience into your biggest content creators? let’s build something viral. explore our tiktok ar gallery:  #tiktokmarketing #augmentedreality #brandedeffects #tiktokar #tiktokbrandedeffects #digitalmarketing #brandstrategy #ugc #alivenow #creativetech #marketinginnovation #arforbusiness</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>AliveNow - Creative Tech Studio</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>stop interacting. start co-creating: why tiktok branded effects are the ultimate roi driver for 2026. the marketing funnel has changed. it’s no longer about getting a user to watch your ad; it’s about getting them to participate in it. if your brand is on tiktok, branded effects are the bridge between passive scrolling and active brand advocacy. at alivenow, we’ve seen first-hand how immersive ar experiences transform digital campaigns into cultural moments. why are branded effects a game-changer for brand managers? unrivaled ugc engine: unlike traditional ads, ar effects invite users to create content for you. this results in authentic, high-volume user generated content that builds trust and virality. low friction, high engagement: no third-party apps. these effects live natively in the tiktok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3d portals. gamification &amp; rewards: from decibel-based challenges to ar sports games, we build experiences that drive real-world actions—like unlocking coupons or entering giveaways. measurable impact: it’s not just "vibes." we track total impressions, effect uses, shares, and engagement data to ensure your campaign delivers a tangible roi. our track record with branded tiktok ar effects: we’ve been busy helping global leaders redefine their tiktok presence. some of our recent work includes: nestlé: a vocal-chord-powered challenge to unlock virtual rewards. mcdonald’s: a delicious ar game catching mccrispy burgers. emirates nbd: celebrating partnerships with immersive gesture-based games. colgate, aldi, and hellman’s: from 3d face morphing to interactive food pairings. the best part? whether it’s a simple 3-day build or a complex 3d world-tracking experience, our team at alivenow handles the entire lifecycle—from concept and design to tiktok platform approval. ready to turn your audience into your biggest content creators? let’s build something viral. explore our tiktok ar gallery:  #tiktokmarketing #augmentedreality #brandedeffects #tiktokar #tiktokbrandedeffects #digitalmarketing #brandstrategy #ugc #alivenow #creativetech #marketinginnovation #arforbusiness</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>13</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>these effects live natively in the tiktok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3d portals. • our track record with branded tiktok ar effects: we’ve been busy helping global leaders redefine their tiktok presence. • start co-creating: why tiktok branded effects are the ultimate roi driver for 2026.</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Salma Mohamed</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>46125.73162333333</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>#Bankers_loan 👨🏻‍💼👩🏻‍💼
 The best rate in the market [18%]👌🔥
@@ -1061,108 +2110,108 @@
 #Kuwait Finance House Bank Egypt</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/salma-mohamed-128584389_bankersabrloan-national-attijariwafa-activity-7449449698714599424-e_wV?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/salma-mohamed-128584389_bankersabrloan-national-attijariwafa-activity-7449449698714599424-e_wV?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>urn:li:activity:7449449698714599424</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>#bankers_loan ‍‍ the best rate in the market [18%] max loan amount: 5,000,000 max tenor: 120 months rate : 18.% decreasing *all tenor* 100% calculation from profits, commission and any variables possibility of paying monthly and annual installments life insurance coverage for free 01070360561 documents required : copy for nid copy business id bank statement 6 months or hr #national bank of egypt (nbe) #attijariwafa bank egypt #alexbank #egbank #first abu dhabi bank (fab) #midbank #banque misr #banque du caire #cib egypt #mashreq #ahli united bank #abu dhabi islamic bank - egypt #abu dhabi commercial bank #emirates nbd #arab bank #bank nxt #saib #arab african international bank #credit agricole egypt #bank abc #national bank of kuwait #hsbc #the united bank of egypt #qnb egypt #arab international bank #al ahli bank of kuwait - egypt #بنك البركة مصر #بنك التعمير والإسكان hd bank #industrial development #bank - idb #faisal islamic bank of egypt #african export-import #bank (afreximbank) #agricultural bank of egypt #central bank of egypt #kuwait finance house bank egypt</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Salma Mohamed</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>#bankers_loan ‍‍ the best rate in the market [18%] max loan amount: 5,000,000 max tenor: 120 months rate : 18.% decreasing *all tenor* 100% calculation from profits, commission and any variables possibility of paying monthly and annual installments life insurance coverage for free 01070360561 documents required : copy for nid copy business id bank statement 6 months or hr #national bank of egypt (nbe) #attijariwafa bank egypt #alexbank #egbank #first abu dhabi bank (fab) #midbank #banque misr #banque du caire #cib egypt #mashreq #ahli united bank #abu dhabi islamic bank - egypt #abu dhabi commercial bank #emirates nbd #arab bank #bank nxt #saib #arab african international bank #credit agricole egypt #bank abc #national bank of kuwait #hsbc #the united bank of egypt #qnb egypt #arab international bank #al ahli bank of kuwait - egypt #بنك البركة مصر #بنك التعمير والإسكان hd bank #industrial development #bank - idb #faisal islamic bank of egypt #african export-import #bank (afreximbank) #agricultural bank of egypt #central bank of egypt #kuwait finance house bank egypt</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Maximum loan amount of 5,000,000 with an 18% decreasing rate. • Loan tenor available up to 120 months with monthly and annual installment options. • Free life insurance coverage included with the loan.</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="R15" t="n">
+        <v>14</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>#bankers_loan ‍‍ the best rate in the market [18%] max loan amount: 5,000,000 max tenor: 120 months rate : 18.% decreasi…</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Ukrainian Business Council Dubai &amp; Northern Emirates</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>46125.72142589121</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Ukrainian Business Council Dubai &amp; Northern Emirates  had the honor of attending a high-level session hosted by Dubai Chambers, in collaboration with Emirates NBD, under the theme “Supporting the Business Community in Navigating Challenging Times.”
 The session brought together key stakeholders from the public and private sectors, including H.E. Mohammad Ali Rashed Lootah, along with senior representatives from leading companies across Dubai.
@@ -1170,224 +2219,224 @@
 We sincerely thank Dubai Chambers for the invitation and for facilitating such a timely and constructive exchange. The Ukrainian Business Council remains committed to strengthening collaboration and supporting the business community in adapting to dynamic global conditions.</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E16" t="n">
         <v>59</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2,785</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ukrainian-business-council-dubai-northern-emirates_ukrainian-business-council-dubai-northern-activity-7449446003285557248-6RYr?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ukrainian-business-council-dubai-northern-emirates_ukrainian-business-council-dubai-northern-activity-7449446003285557248-6RYr?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>urn:li:activity:7449446003285557248</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>ukrainian business council dubai &amp; northern emirates had the honor of attending a high-level session hosted by dubai chambers, in collaboration with emirates nbd, under the theme “supporting the business community in navigating challenging times.” the session brought together key stakeholders from the public and private sectors, including h.e. mohammad ali rashed lootah, along with senior representatives from leading companies across dubai. this important dialogue provided valuable insights into the evolving economic landscape and addressed the current challenges faced by businesses, while highlighting practical approaches to resilience and growth. we sincerely thank dubai chambers for the invitation and for facilitating such a timely and constructive exchange. the ukrainian business council remains committed to strengthening collaboration and supporting the business community in adapting to dynamic global conditions.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Ukrainian Business Council Dubai &amp; Northern Emirates</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>ukrainian business council dubai &amp; northern emirates had the honor of attending a high-level session hosted by dubai chambers, in collaboration with emirates nbd, under the theme “supporting the business community in navigating challenging times.” the session brought together key stakeholders from the public and private sectors, including h.e. mohammad ali rashed lootah, along with senior representatives from leading companies across dubai. this important dialogue provided valuable insights into the evolving economic landscape and addressed the current challenges faced by businesses, while highlighting practical approaches to resilience and growth. we sincerely thank dubai chambers for the invitation and for facilitating such a timely and constructive exchange. the ukrainian business council remains committed to strengthening collaboration and supporting the business community in adapting to dynamic global conditions.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>High-level session focused on supporting businesses during challenging times. • Key stakeholders from public and private sectors participated. • Discussion included insights on economic challenges and resilience strategies.</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="R16" t="n">
+        <v>15</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>the ukrainian business council remains committed to strengthening collaboration and supporting the business community in adapting to dynamic global conditions. • mohammad ali rashed lootah, along with senior representatives from leading companies across dubai. • we sincerely thank dubai chambers for the invitation and for facilitating such a timely and constructive exchange.</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Dubai Cares</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>46125.71291104166</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>A few clicks. A child’s future changed. Emirates NBD has made it so easy for its customers to donate to Dubai Cares through its app, helping support children’s education globally.  #DubaiCares #ENBD #EducationForAll
 ببضع نقرات، تستطيع تغيير مستقبل طفل. قام بنك الإمارات دبي الوطني (ENBD) بتسهيل عملية التبرع لدبي العطاء من خلال تطبيقه، مما يساهم في دعم تعليم الأطفال حول العالم.
 #دبي_العطاء #ENBD #التعليم_للجميع</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E17" t="n">
         <v>11</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>linkedinVideo</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>51,339</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/dubaicares_dubaicares-enbd-educationforall-activity-7449442917607358464-jSlu?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/dubaicares_dubaicares-enbd-educationforall-activity-7449442917607358464-jSlu?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>urn:li:activity:7449442917607358464</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>a few clicks. a child’s future changed. emirates nbd has made it so easy for its customers to donate to dubai cares through its app, helping support children’s education globally. #dubaicares #enbd #educationforall ببضع نقرات، تستطيع تغيير مستقبل طفل. قام بنك الإمارات دبي الوطني (enbd) بتسهيل عملية التبرع لدبي العطاء من خلال تطبيقه، مما يساهم في دعم تعليم الأطفال حول العالم. #دبي_العطاء #enbd #التعليم_للجميع</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Dubai Cares</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>a few clicks. a child’s future changed. emirates nbd has made it so easy for its customers to donate to dubai cares through its app, helping support children’s education globally. #dubaicares #enbd #educationforall ببضع نقرات، تستطيع تغيير مستقبل طفل. قام بنك الإمارات دبي الوطني (enbd) بتسهيل عملية التبرع لدبي العطاء من خلال تطبيقه، مما يساهم في دعم تعليم الأطفال حول العالم. #دبي_العطاء #enbd #التعليم_للجميع</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Emirates NBD enables easy donations to Dubai Cares via its app. • Donations support children's education globally. • Initiative promotes education for all.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="R17" t="n">
+        <v>16</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>emirates nbd has made it so easy for its customers to donate to dubai cares through its app, helping support children’s education globally. • #dubaicares #enbd #educationforall ببضع نقرات، تستطيع تغيير مستقبل طفل. • a child’s future changed.</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Global Executive</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C18" s="2" t="n">
         <v>46125.69042440972</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Spotlighting Professional Leadership: Alaa Algain 🌟
 She serves as Customer Service Executive at Emirates NBD, bringing expertise in retail banking customer service, sales, liability management, priority banking, and customer experience, with progressive roles including Branch Sales Executive and Liability Agent, holding a Bachelor of Science in Economics &amp; Administration from King AbdulAziz University, certified in Customer Focus and Customer Satisfaction Training and Customer Experience Journey.
@@ -1396,112 +2445,112 @@
 #CustomerServiceExecutive #EmiratesNBD #RetailBanking #CustomerExperience #SalesExecutive #LiabilityManagement #PriorityBanking #KingAbdulAzizUniversity #SaudiArabia #WomenInBanking</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>51</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E18" t="n">
+        <v>52</v>
+      </c>
+      <c r="F18" t="n">
         <v>8</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>19,117</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/theglobal-executive_customerserviceexecutive-emiratesnbd-retailbanking-activity-7449434768724668416-Sq9k?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/theglobal-executive_customerserviceexecutive-emiratesnbd-retailbanking-activity-7449434768724668416-Sq9k?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>urn:li:activity:7449434768724668416</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>spotlighting professional leadership: alaa algain she serves as customer service executive at emirates nbd, bringing expertise in retail banking customer service, sales, liability management, priority banking, and customer experience, with progressive roles including branch sales executive and liability agent, holding a bachelor of science in economics &amp; administration from king abdulaziz university, certified in customer focus and customer satisfaction training and customer experience journey. we honor alaa algain for her ambition, organizational excellence, time management, and commitment to delivering exceptional customer service and building strong client relationships across saudi arabia's banking sector. want to share your inspiring story? contact us on whatsapp:  #customerserviceexecutive #emiratesnbd #retailbanking #customerexperience #salesexecutive #liabilitymanagement #prioritybanking #kingabdulazizuniversity #saudiarabia #womeninbanking</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Global Executive</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>spotlighting professional leadership: alaa algain she serves as customer service executive at emirates nbd, bringing expertise in retail banking customer service, sales, liability management, priority banking, and customer experience, with progressive roles including branch sales executive and liability agent, holding a bachelor of science in economics &amp; administration from king abdulaziz university, certified in customer focus and customer satisfaction training and customer experience journey. we honor alaa algain for her ambition, organizational excellence, time management, and commitment to delivering exceptional customer service and building strong client relationships across saudi arabia's banking sector. want to share your inspiring story? contact us on whatsapp:  #customerserviceexecutive #emiratesnbd #retailbanking #customerexperience #salesexecutive #liabilitymanagement #prioritybanking #kingabdulazizuniversity #saudiarabia #womeninbanking</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>8</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Alaa Algain is a Customer Service Executive at Emirates NBD. • She holds a Bachelor of Science in Economics &amp; Administration from King Abdulaziz University. • Recognized for her commitment to exceptional customer service in Saudi Arabia's banking sector.</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="R18" t="n">
+        <v>17</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>want to share your inspiring story?</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Eslam Essam</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>46125.68512021991</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Forbes just ranked the UAE's 10 most valuable companies for 2026.
 Combined market cap: $692.3 billion.
@@ -1527,108 +2576,108 @@
 #UAErealestate #Emaar #Dubai #RealEstate #PropertyInvestment #UAE #Forbes</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E19" t="n">
         <v>36</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/eslamessamdxb_uaerealestate-emaar-dubai-activity-7449432846550679552-Rgjv?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/eslamessamdxb_uaerealestate-emaar-dubai-activity-7449432846550679552-Rgjv?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>urn:li:activity:7449432846550679552</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>forbes just ranked the uae's 10 most valuable companies for 2026. combined market cap: $692.3 billion. one name on that list stands out differently for anyone in real estate: emaar. $36.1 billion. #8 in the entire uae economy. think about what that means. in a list dominated by energy giants (taqa $87.9b, adnoc gas $75.4b) and banking powerhouses (fab $56b, emirates nbd $53.5b) — a real estate developer holds its own among the most valuable companies in one of the world's fastest-growing economies. that's not a coincidence. that's a signal. here's what emaar's position tells me about the uae real estate market: → real estate isn't a sector here — it's infrastructure. emaar built downtown dubai. dubai mall. burj khalifa. address hotels. these aren't properties — they're the physical backbone of a global city. → demand is structural, not cyclical. when a developer reaches $36b in market cap, it's because the market it operates in has sustained, compounding demand — not a temporary boom. → the capital is already here. ihc ($238.6b), taqa ($87.9b), adnoc gas ($75.4b) — the wealth sitting above emaar on this list doesn't leave the uae. it circulates. real estate is where a significant portion of that circulation lands. → this is still early. the uae ranked #1 and #2 globally for startup and sme friendliness in 2026. every company that forms here needs space — offices, retail, mixed-use, residential. emaar builds exactly that. for anyone working in uae real estate: the fundamentals aren't just strong. they're institutionally validated. $36.1 billion says so. source: forbes middle east — data as of january 31, 2026 #uaerealestate #emaar #dubai #realestate #propertyinvestment #uae #forbes</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Eslam Essam</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>forbes just ranked the uae's 10 most valuable companies for 2026. combined market cap: $692.3 billion. one name on that list stands out differently for anyone in real estate: emaar. $36.1 billion. #8 in the entire uae economy. think about what that means. in a list dominated by energy giants (taqa $87.9b, adnoc gas $75.4b) and banking powerhouses (fab $56b, emirates nbd $53.5b) — a real estate developer holds its own among the most valuable companies in one of the world's fastest-growing economies. that's not a coincidence. that's a signal. here's what emaar's position tells me about the uae real estate market: → real estate isn't a sector here — it's infrastructure. emaar built downtown dubai. dubai mall. burj khalifa. address hotels. these aren't properties — they're the physical backbone of a global city. → demand is structural, not cyclical. when a developer reaches $36b in market cap, it's because the market it operates in has sustained, compounding demand — not a temporary boom. → the capital is already here. ihc ($238.6b), taqa ($87.9b), adnoc gas ($75.4b) — the wealth sitting above emaar on this list doesn't leave the uae. it circulates. real estate is where a significant portion of that circulation lands. → this is still early. the uae ranked #1 and #2 globally for startup and sme friendliness in 2026. every company that forms here needs space — offices, retail, mixed-use, residential. emaar builds exactly that. for anyone working in uae real estate: the fundamentals aren't just strong. they're institutionally validated. $36.1 billion says so. source: forbes middle east — data as of january 31, 2026 #uaerealestate #emaar #dubai #realestate #propertyinvestment #uae #forbes</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>9</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Emaar is ranked #8 among UAE's most valuable companies with a market cap of $36.1 billion. • UAE's combined market cap for top 10 companies is $692.3 billion. • Real estate in the UAE is viewed as essential infrastructure, not just a sector.</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="R19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>here's what emaar's position tells me about the uae real estate market: → real estate isn't a sector here — it's infrastructure. • ihc ($238.6b), taqa ($87.9b), adnoc gas ($75.4b) — the wealth sitting above emaar on this list doesn't leave the uae. • forbes just ranked the uae's 10 most valuable companies for 2026.</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Ayaz Uddin</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C20" s="2" t="n">
         <v>46125.6721824074</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>🚀 Excited to share Sahala (سهلة) — a UI/UX concept I've been working on.
 Sahala is a unified super-app designed for UAE residents to manage government services, visa tracking, utility payments, and identity documents — all in one place, in both English and Arabic.
@@ -1645,108 +2694,108 @@
 #UIUX #ProductDesign #MobileDesign #DesignSystem #UAE #GovTech #FigmaDesign #UXDesign #RTL #BilingualDesign #AppDesign #userexperiencedesign #Userinterfacedesign</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E20" t="n">
         <v>8</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>linkedinVideo</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ayaz-uddin-a115651a5_uiux-productdesign-mobiledesign-activity-7449428158044442624-Teyt?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ayaz-uddin-a115651a5_uiux-productdesign-mobiledesign-activity-7449428158044442624-Teyt?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>urn:li:activity:7449428158044442624</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>excited to share sahala (سهلة) — a ui/ux concept i've been working on. sahala is a unified super-app designed for uae residents to manage government services, visa tracking, utility payments, and identity documents — all in one place, in both english and arabic. here's what i designed end-to-end: 6 core modules — dashboard, visa, payments, services, profile &amp; document vault mobile-first at 375px, fully responsive up to 1440px desktop complete bilingual experience — english ltr &amp; arabic rtl with a single toggle custom design system — deep petrol blue + desert gold palette, glassmorphism components, and a 4px spacing scale biometric document vault — upload once, attach to any application instantly 3-step service application flow covering 8 uae government services including golden visa renewal, ejari, dewa, and emirates id this project pushed me across every layer of product design — from information architecture and user flows to visual design, accessibility (wcag 3.0), and interactive prototyping. would love to hear your thoughts! dicetek llc emirates nbd emirates dp world dubai holding enoc dubai electricity &amp; water authority - dewa adnoc group abu dhabi commercial bank landmark group majid al futtaim #uiux #productdesign #mobiledesign #designsystem #uae #govtech #figmadesign #uxdesign #rtl #bilingualdesign #appdesign #userexperiencedesign #userinterfacedesign</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Ayaz Uddin</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>excited to share sahala (سهلة) — a ui/ux concept i've been working on. sahala is a unified super-app designed for uae residents to manage government services, visa tracking, utility payments, and identity documents — all in one place, in both english and arabic. here's what i designed end-to-end: 6 core modules — dashboard, visa, payments, services, profile &amp; document vault mobile-first at 375px, fully responsive up to 1440px desktop complete bilingual experience — english ltr &amp; arabic rtl with a single toggle custom design system — deep petrol blue + desert gold palette, glassmorphism components, and a 4px spacing scale biometric document vault — upload once, attach to any application instantly 3-step service application flow covering 8 uae government services including golden visa renewal, ejari, dewa, and emirates id this project pushed me across every layer of product design — from information architecture and user flows to visual design, accessibility (wcag 3.0), and interactive prototyping. would love to hear your thoughts! dicetek llc emirates nbd emirates dp world dubai holding enoc dubai electricity &amp; water authority - dewa adnoc group abu dhabi commercial bank landmark group majid al futtaim #uiux #productdesign #mobiledesign #designsystem #uae #govtech #figmadesign #uxdesign #rtl #bilingualdesign #appdesign #userexperiencedesign #userinterfacedesign</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Sahala is a unified super-app for UAE residents managing government services. • Features 6 core modules including visa tracking and utility payments. • Offers a complete bilingual experience in English and Arabic.</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="R20" t="n">
+        <v>19</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>sahala is a unified super-app designed for uae residents to manage government services, visa tracking, utility payments, and identity documents — all in one place, in both english and arabic. • excited to share sahala (سهلة) — a ui/ux concept i've been working on. • would love to hear your thoughts!</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Forbes Middle East</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C21" s="2" t="n">
         <v>46125.66993076389</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>The UAE’s top 10 most valuable companies have a combined market capitalization of $692.3 billion. IHC leads the group, accounting for over 34% of the total value, while the banks and financial services sector is the most represented with three entries.
 #Forbes
@@ -1754,112 +2803,112 @@
 IHC TAQA GroupADNOC Gas First Abu Dhabi Bank (FAB) Emirates NBD e&amp; Dubai Electricity &amp; Water Authority - DEWA Abu Dhabi Commercial Bank Emaar Alpha Dhabi Holding</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>373</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="E21" t="n">
+        <v>375</v>
+      </c>
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G21" t="n">
+        <v>35</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>363,068</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/forbesmiddleeast_forbes-activity-7449427342076153856-wXUE?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>363,072</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/forbesmiddleeast_forbes-activity-7449427342076153856-wXUE?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>urn:li:activity:7449427342076153856</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>the uae’s top 10 most valuable companies have a combined market capitalization of $692.3 billion. ihc leads the group, accounting for over 34% of the total value, while the banks and financial services sector is the most represented with three entries. #forbes for more details:  ihc taqa groupadnoc gas first abu dhabi bank (fab) emirates nbd e&amp; dubai electricity &amp; water authority - dewa abu dhabi commercial bank emaar alpha dhabi holding</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Forbes Middle East</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>the uae’s top 10 most valuable companies have a combined market capitalization of $692.3 billion. ihc leads the group, accounting for over 34% of the total value, while the banks and financial services sector is the most represented with three entries. #forbes for more details:  ihc taqa groupadnoc gas first abu dhabi bank (fab) emirates nbd e&amp; dubai electricity &amp; water authority - dewa abu dhabi commercial bank emaar alpha dhabi holding</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>11</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>UAE's top 10 companies have a combined market cap of $692.3 billion. • IHC accounts for over 34% of the total market value. • The banks and financial services sector has three entries in the top 10.</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="R21" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>#forbes for more details: ihc taqa groupadnoc gas first abu dhabi bank (fab) emirates nbd e&amp; dubai electricity &amp; water authority - dewa abu dhabi commercial bank emaar alpha dhabi holding • the uae’s top 10 most valuable companies have a combined market capitalization of $692.3 billion. • ihc leads the group, accounting for over 34% of the total value, while the banks and financial services sector is the most represented with three entries.</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>FactsBay</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C22" s="2" t="n">
         <v>46125.66832425926</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>🔍 RBL Bank–Emirates NBD Deal: A Strategic Shift in India’s Banking Landscape
 RBL Bank is moving forward with a critical phase of its partnership with Emirates NBD, seeking shareholder approval for key amendments tied to governance and ownership structure.
@@ -1876,112 +2925,112 @@
 #Banking #Leadership #Strategy #FDI #IndianEconomy #CorporateGovernance #Finance #BusinessNews</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/factsbay_banking-leadership-strategy-activity-7449426759898537984-53-8?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/factsbay_banking-leadership-strategy-activity-7449426759898537984-53-8?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>urn:li:activity:7449426759898537984</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>rbl bank–emirates nbd deal: a strategic shift in india’s banking landscape rbl bank is moving forward with a critical phase of its partnership with emirates nbd, seeking shareholder approval for key amendments tied to governance and ownership structure. following regulatory clearance from the reserve bank of india, emirates nbd is set to acquire a majority stake of up to 74%, marking one of the most significant foreign investments in india’s banking sector. to align with rbi conditions, rbl bank’s board has approved changes to: • articles of association and governance framework • board composition and director nomination rights • overall structure as it transitions toward a foreign bank subsidiary model an extraordinary general meeting (egm) has been scheduled, where shareholders will vote on these crucial proposals—making this a defining moment for the bank’s future direction. why this matters: this deal reflects growing global confidence in india’s financial sector and highlights how cross-border partnerships are reshaping banking through capital infusion, governance evolution, and global integration. read the full analysis:  #banking #leadership #strategy #fdi #indianeconomy #corporategovernance #finance #businessnews</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>FactsBay</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>rbl bank–emirates nbd deal: a strategic shift in india’s banking landscape rbl bank is moving forward with a critical phase of its partnership with emirates nbd, seeking shareholder approval for key amendments tied to governance and ownership structure. following regulatory clearance from the reserve bank of india, emirates nbd is set to acquire a majority stake of up to 74%, marking one of the most significant foreign investments in india’s banking sector. to align with rbi conditions, rbl bank’s board has approved changes to: • articles of association and governance framework • board composition and director nomination rights • overall structure as it transitions toward a foreign bank subsidiary model an extraordinary general meeting (egm) has been scheduled, where shareholders will vote on these crucial proposals—making this a defining moment for the bank’s future direction. why this matters: this deal reflects growing global confidence in india’s financial sector and highlights how cross-border partnerships are reshaping banking through capital infusion, governance evolution, and global integration. read the full analysis:  #banking #leadership #strategy #fdi #indianeconomy #corporategovernance #finance #businessnews</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>12</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Emirates NBD to acquire up to 74% stake in RBL Bank. • RBL Bank's board approved changes to governance and ownership structure. • Extraordinary general meeting scheduled for shareholder vote on key proposals.</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="R22" t="n">
+        <v>21</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>read the full analysis: #banking #leadership #strategy #fdi #indianeconomy #corporategovernance #finance #businessnews</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Soko Directory Investments Limited</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C23" s="2" t="n">
         <v>46125.66651456019</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>As geopolitical tensions ripple across the Middle East amid the ongoing conflict between the United States, Israel and Iran, Dubai is stepping up economic support measures and reinforcing financial stability to sustain confidence, stabilise markets, and keep business moving.
 Even as the region grapples with uncertainty, the emirate is projecting a message that has defined its rise as a global hub: resilience is not reactive but engineered through policy coordination, diversified growth, and rapid institutional response.
@@ -1989,112 +3038,112 @@
 https://lnkd.in/dY58XnZZ</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1,960</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/soko-directory-investments_dubai-shields-economy-as-regional-conflict-activity-7449426104085454848-87Nb?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADgAIKYBbY63vzTqLD7CnZCdTY5AtXdekfw</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1,961</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/soko-directory-investments_dubai-shields-economy-as-regional-conflict-activity-7449426104085454848-87Nb?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>urn:li:activity:7449426104085454848</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>as geopolitical tensions ripple across the middle east amid the ongoing conflict between the united states, israel and iran, dubai is stepping up economic support measures and reinforcing financial stability to sustain confidence, stabilise markets, and keep business moving. even as the region grapples with uncertainty, the emirate is projecting a message that has defined its rise as a global hub: resilience is not reactive but engineered through policy coordination, diversified growth, and rapid institutional response. at the centre of this response is a coordinated intervention involving government institutions, financial regulators, and the private sector. emirates nbd, one of the region’s largest banking groups, has introduced a business support package targeting small and medium-sized enterprises (smes), widely regarded as the backbone of dubai’s economy.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Soko Directory Investments Limited</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>as geopolitical tensions ripple across the middle east amid the ongoing conflict between the united states, israel and iran, dubai is stepping up economic support measures and reinforcing financial stability to sustain confidence, stabilise markets, and keep business moving. even as the region grapples with uncertainty, the emirate is projecting a message that has defined its rise as a global hub: resilience is not reactive but engineered through policy coordination, diversified growth, and rapid institutional response. at the centre of this response is a coordinated intervention involving government institutions, financial regulators, and the private sector. emirates nbd, one of the region’s largest banking groups, has introduced a business support package targeting small and medium-sized enterprises (smes), widely regarded as the backbone of dubai’s economy.</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>13</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Dubai is enhancing economic support amid Middle East geopolitical tensions. • Emirates NBD launched a business support package for small and medium-sized enterprises. • The emirate emphasizes resilience through policy coordination and diversified growth.</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="R23" t="n">
+        <v>22</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>at the centre of this response is a coordinated intervention involving government institutions, financial regulators, and the private sector.</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Bindhu Nair</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C24" s="2" t="n">
         <v>46126.43434784722</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>𝐋𝐚𝐬𝐭 𝐂𝐚𝐥𝐥 𝐟𝐨𝐫 𝐒𝐩𝐨𝐧𝐬𝐨𝐫𝐬 - 𝐂𝐨𝐥𝐨𝐫 𝐒𝐩𝐥𝐚𝐬𝐡
 Over the past few weeks, I've been in conversations with several brands interested in being part of Color Splash.
@@ -2111,108 +3160,108 @@
 noon BAIC Automobile SA KIA Motors Porsche Middle East and Africa FZE Royal Health Group AE Etihad Emirates Emirates NBD e&amp; UAE ADNOC Group Al Ain Farms Al Ain Hospital Burjeel Hospital Burjeel Holdings RAG Holdings</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/bindunair77_%F0%9D%90%8B%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%90%82%F0%9D%90%9A%F0%9D%90%A5%F0%9D%90%A5-%F0%9D%90%9F%F0%9D%90%A8%F0%9D%90%AB-%F0%9D%90%92%F0%9D%90%A9%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%AC%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%AC-activity-7449704357551403008-zQfz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/bindunair77_%F0%9D%90%8B%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%90%82%F0%9D%90%9A%F0%9D%90%A5%F0%9D%90%A5-%F0%9D%90%9F%F0%9D%90%A8%F0%9D%90%AB-%F0%9D%90%92%F0%9D%90%A9%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%AC%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%AC-activity-7449704357551403008-zQfz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>urn:li:activity:7449704357551403008</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>- over the past few weeks, i've been in conversations with several brands interested in being part of color splash. as we move into the final stage of planning, we're now closing sponsor partnerships. color splash is shaping up to be a large-scale cultural experience featuring: thousands of attendees ‍‍‍ families &amp; communities professionals &amp; decision-makers entertainment &amp; live experiences brand activations &amp; engagement opportunities for brands, this is more than visibility, it's an opportunity to connect meaningfully with people. ⏳ sponsor slots will be closing by the end of this week dm "sponsor" to get all the details noon baic automobile sa kia motors porsche middle east and africa fze royal health group ae etihad emirates emirates nbd e&amp; uae adnoc group al ain farms al ain hospital burjeel hospital burjeel holdings rag holdings</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Bindhu Nair</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>- over the past few weeks, i've been in conversations with several brands interested in being part of color splash. as we move into the final stage of planning, we're now closing sponsor partnerships. color splash is shaping up to be a large-scale cultural experience featuring: thousands of attendees ‍‍‍ families &amp; communities professionals &amp; decision-makers entertainment &amp; live experiences brand activations &amp; engagement opportunities for brands, this is more than visibility, it's an opportunity to connect meaningfully with people. ⏳ sponsor slots will be closing by the end of this week dm "sponsor" to get all the details noon baic automobile sa kia motors porsche middle east and africa fze royal health group ae etihad emirates emirates nbd e&amp; uae adnoc group al ain farms al ain hospital burjeel hospital burjeel holdings rag holdings</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>14</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Closing sponsor partnerships for Color Splash by the end of this week. • Event will feature thousands of attendees, including families and professionals. • Participating brands will have meaningful engagement opportunities.</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
+      <c r="R24" t="n">
+        <v>23</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>- over the past few weeks, i've been in conversations with several brands interested in being part of color splash. • as we move into the final stage of planning, we're now closing sponsor partnerships.</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Ameer Akhtar</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>46126.41214994213</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Last week, the UAE stock market had its biggest single-day move since March 2020.
 AED 125 billion added to market capitalisation in one day. Dubai's index up 6.9%. Abu Dhabi up 2.8%. Emaar up 13%. Emirates NBD, Air Arabia, Salik — all up more than 10%.
@@ -2231,216 +3280,216 @@
 #ADX #UAE #DFM #markets #recovery</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ameerakhtar_adx-uae-dfm-activity-7449696313299881984-C5Dp?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ameerakhtar_adx-uae-dfm-activity-7449696313299881984-C5Dp?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>urn:li:activity:7449696313299881984</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>last week, the uae stock market had its biggest single-day move since march 2020. aed 125 billion added to market capitalisation in one day. dubai's index up 6.9%. abu dhabi up 2.8%. emaar up 13%. emirates nbd, air arabia, salik — all up more than 10%. markets move fast. we knew that. but here is what the numbers do not show. behind every index point that moved yesterday is a business owner who can now make a decision they had been sitting on for weeks. a retailer who can reorder stock with confidence. a family that can stop quietly recalculating what they can and cannot afford this month. a marketing team that can finally get budget approved for a campaign that has been in draft since the tension started. consumer confidence does not recover the same day the markets do. markets are a signal. consumer behaviour is a response — and responses take longer. the businesses that understand this distinction are the ones that will move first, spend smartest and capture the most ground in the window between the market reacting and the public catching up. that window is open right now. the ceasefire has acted as a catalyst. investor sentiment has shifted. airspace is reopening. tourism and key industries are beginning to breathe again. but sentiment is not the same as certainty. one analyst noted the market could see further volatility as geopolitical headlines continue to develop. so the question for every marketer, business owner and brand in this region is not "did the market go up?" it is — "what are you doing in the next 30 days while your competitors are still exhaling?" the window between a market recovery and a consumer recovery is where brands are built. are you in it? #adx #uae #dfm #markets #recovery</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Ameer Akhtar</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>last week, the uae stock market had its biggest single-day move since march 2020. aed 125 billion added to market capitalisation in one day. dubai's index up 6.9%. abu dhabi up 2.8%. emaar up 13%. emirates nbd, air arabia, salik — all up more than 10%. markets move fast. we knew that. but here is what the numbers do not show. behind every index point that moved yesterday is a business owner who can now make a decision they had been sitting on for weeks. a retailer who can reorder stock with confidence. a family that can stop quietly recalculating what they can and cannot afford this month. a marketing team that can finally get budget approved for a campaign that has been in draft since the tension started. consumer confidence does not recover the same day the markets do. markets are a signal. consumer behaviour is a response — and responses take longer. the businesses that understand this distinction are the ones that will move first, spend smartest and capture the most ground in the window between the market reacting and the public catching up. that window is open right now. the ceasefire has acted as a catalyst. investor sentiment has shifted. airspace is reopening. tourism and key industries are beginning to breathe again. but sentiment is not the same as certainty. one analyst noted the market could see further volatility as geopolitical headlines continue to develop. so the question for every marketer, business owner and brand in this region is not "did the market go up?" it is — "what are you doing in the next 30 days while your competitors are still exhaling?" the window between a market recovery and a consumer recovery is where brands are built. are you in it? #adx #uae #dfm #markets #recovery</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>15</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>UAE stock market added AED 125 billion in a single day. • Dubai's index rose 6.9%, Abu Dhabi's by 2.8%. • Market recovery does not equal immediate consumer confidence.</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="R25" t="n">
+        <v>24</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>last week, the uae stock market had its biggest single-day move since march 2020. • behind every index point that moved yesterday is a business owner who can now make a decision they had been sitting on for weeks. • the businesses that understand this distinction are the ones that will move first, spend smartest and capture the most ground in the window between the market reacting and the public catching up.</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Futoon Alburaidi, CertIFR</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>46126.40769878472</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>I’m pleased to share that I have successfully completed the Management &amp; Supervision Skills training program delivered by The Financial Academy. 
 I would like to extend my appreciation to Emirates NBD for providing me with this valuable opportunity. The program was truly enriching and has contributed greatly to enhancing my professional skills.
 Really great session by Mervana Gad , PMP® .</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E26" t="n">
+        <v>16</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/futoon-alburaidi-certifr-1690541b8_im-pleased-to-share-that-i-have-successfully-activity-7449694700254556160-FjZf?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/futoon-alburaidi-certifr-1690541b8_im-pleased-to-share-that-i-have-successfully-activity-7449694700254556160-FjZf?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>urn:li:activity:7449694700254556160</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>i’m pleased to share that i have successfully completed the management &amp; supervision skills training program delivered by the financial academy. i would like to extend my appreciation to emirates nbd for providing me with this valuable opportunity. the program was truly enriching and has contributed greatly to enhancing my professional skills. really great session by mervana gad , pmp® .</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Futoon Alburaidi, CertIFR</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>i’m pleased to share that i have successfully completed the management &amp; supervision skills training program delivered by the financial academy. i would like to extend my appreciation to emirates nbd for providing me with this valuable opportunity. the program was truly enriching and has contributed greatly to enhancing my professional skills. really great session by mervana gad , pmp® .</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R17" t="n">
-        <v>16</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Completed management &amp; supervision skills training program at the financial academy. • Appreciated Emirates NBD for the opportunity. • Training session led by Mervana Gad, PMP®.</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="R26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>i’m pleased to share that i have successfully completed the management &amp; supervision skills training program delivered by the financial academy. • the program was truly enriching and has contributed greatly to enhancing my professional skills. • i would like to extend my appreciation to emirates nbd for providing me with this valuable opportunity.</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Abdul Shakeeb</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C27" s="2" t="n">
         <v>46126.35973930555</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>UAE Residents — Don’t Miss This!
 Still paying high EMIs or not using the right credit card? You might be leaving money on the table.
@@ -2460,108 +3509,108 @@
 #UAEBanking #LoansUAE #CreditCardsUAE #FinanceDubai #EmiratesNBD #SmartMoney #FinancialGoals #DubaiLife #MoneyMatters</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/abdulshakeeb_uaebanking-loansuae-creditcardsuae-activity-7449677320321277952-Wf3x?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abdulshakeeb_uaebanking-loansuae-creditcardsuae-activity-7449677320321277952-Wf3x?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>urn:li:activity:7449677320321277952</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>uae residents — don’t miss this! still paying high emis or not using the right credit card? you might be leaving money on the table. switch smarter with: personal loans at better rates easy buyouts to reduce your burden credit cards with real lifestyle benefits all through an emirates nbd channel partner — fast, simple &amp; tailored for you. ⏳ offers valid only till april 30th, 2026 this is your chance to save more, spend smarter and plan better. dm now to check your eligibility — it takes just a few minutes! approvals are subject to central bank guidelines &amp; individual credit history. abdul shakeeb relationship officer emirates nbd channel partner 0525114342 #uaebanking #loansuae #creditcardsuae #financedubai #emiratesnbd #smartmoney #financialgoals #dubailife #moneymatters</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Abdul Shakeeb</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>uae residents — don’t miss this! still paying high emis or not using the right credit card? you might be leaving money on the table. switch smarter with: personal loans at better rates easy buyouts to reduce your burden credit cards with real lifestyle benefits all through an emirates nbd channel partner — fast, simple &amp; tailored for you. ⏳ offers valid only till april 30th, 2026 this is your chance to save more, spend smarter and plan better. dm now to check your eligibility — it takes just a few minutes! approvals are subject to central bank guidelines &amp; individual credit history. abdul shakeeb relationship officer emirates nbd channel partner 0525114342 #uaebanking #loansuae #creditcardsuae #financedubai #emiratesnbd #smartmoney #financialgoals #dubailife #moneymatters</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>17</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Personal loans available at better rates through Emirates NBD channel partner. • Offers valid until April 30th, 2026. • Eligibility checks take just a few minutes.</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
+      <c r="R27" t="n">
+        <v>26</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>abdul shakeeb relationship officer emirates nbd channel partner 0525114342 #uaebanking #loansuae #creditcardsuae #financedubai #emiratesnbd #smartmoney #financialgoals #dubailife #moneymatters • ⏳ offers valid only till april 30th, 2026 this is your chance to save more, spend smarter and plan better. • still paying high emis or not using the right credit card?</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>CTC Tax and Accounting</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C28" s="2" t="n">
         <v>46126.35433054398</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Supporting Businesses in Uncertain Times 🇦🇪
 In today’s environment, managing cash flow and planning ahead has become a top priority for businesses across the UAE.
@@ -2593,112 +3642,112 @@
 For businesses, the key is to stay informed and proactive: opportunities for support are available, but they often need to be activated.</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E28" t="n">
         <v>1</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>6,480</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ct-consultancy_supporting-businesses-in-uncertain-times-activity-7449675360251695104-Awcx?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ct-consultancy_supporting-businesses-in-uncertain-times-activity-7449675360251695104-Awcx?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>urn:li:activity:7449675360251695104</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>supporting businesses in uncertain times in today’s environment, managing cash flow and planning ahead has become a top priority for businesses across the uae. the good news? support is coming from multiple directions: banks, government initiatives, and even large ecosystem players are stepping in to ease the pressure. banking support: easing day-to-day pressure several banks have already introduced measures to help businesses better manage their liquidity. for instance, emirates nbd has launched a fee relief package, reducing or waiving selected banking fees. at a broader level, the central bank of the uae has injected additional liquidity into the banking system. in practical terms, this ensures that banks can continue lending and supporting businesses, even during uncertain periods. this might be the right time to speak to your bank. there may be relief options or flexibility available that you are not yet leveraging. rent relief &amp; ecosystem support support is not limited to financial institutions. large companies and free zones are also taking concrete steps to assist smaller businesses within their ecosystems. across the uae, several initiatives include: - rent relief - cash allowances - more flexible payment terms for example, dubai south has introduced practical measures such as: - rent-free periods (up to 3 months in some cases) - payment deferrals - waiver of administrative penalties - stable rental rates (no increases) similarly, dubai international financial centre has implemented: - installment plans for rent and fees - grace periods on certain charges - increased cost flexibility these measures directly reduce short-term cash outflows and help businesses preserve liquidity. looking ahead: tax incentives for innovation beyond short-term relief, the uae is also encouraging long-term resilience through innovation. a new scheme allows businesses to benefit from up to 50% tax credit on r&amp;d expenses, capped at aed 5 million. for businesses, the key is to stay informed and proactive: opportunities for support are available, but they often need to be activated.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>CTC Tax and Accounting</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>supporting businesses in uncertain times in today’s environment, managing cash flow and planning ahead has become a top priority for businesses across the uae. the good news? support is coming from multiple directions: banks, government initiatives, and even large ecosystem players are stepping in to ease the pressure. banking support: easing day-to-day pressure several banks have already introduced measures to help businesses better manage their liquidity. for instance, emirates nbd has launched a fee relief package, reducing or waiving selected banking fees. at a broader level, the central bank of the uae has injected additional liquidity into the banking system. in practical terms, this ensures that banks can continue lending and supporting businesses, even during uncertain periods. this might be the right time to speak to your bank. there may be relief options or flexibility available that you are not yet leveraging. rent relief &amp; ecosystem support support is not limited to financial institutions. large companies and free zones are also taking concrete steps to assist smaller businesses within their ecosystems. across the uae, several initiatives include: - rent relief - cash allowances - more flexible payment terms for example, dubai south has introduced practical measures such as: - rent-free periods (up to 3 months in some cases) - payment deferrals - waiver of administrative penalties - stable rental rates (no increases) similarly, dubai international financial centre has implemented: - installment plans for rent and fees - grace periods on certain charges - increased cost flexibility these measures directly reduce short-term cash outflows and help businesses preserve liquidity. looking ahead: tax incentives for innovation beyond short-term relief, the uae is also encouraging long-term resilience through innovation. a new scheme allows businesses to benefit from up to 50% tax credit on r&amp;d expenses, capped at aed 5 million. for businesses, the key is to stay informed and proactive: opportunities for support are available, but they often need to be activated.</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>18</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Banks in the UAE are offering liquidity support and fee relief packages. • Large companies are providing rent relief and flexible payment terms to smaller businesses. • A new scheme offers up to 50% tax credit on R&amp;D expenses, capped at AED 5 million.</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
+      <c r="R28" t="n">
+        <v>27</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>supporting businesses in uncertain times in today’s environment, managing cash flow and planning ahead has become a top priority for businesses across the uae. • banking support: easing day-to-day pressure several banks have already introduced measures to help businesses better manage their liquidity. • looking ahead: tax incentives for innovation beyond short-term relief, the uae is also encouraging long-term resilience through innovation.</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B20" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Simanta Das</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C29" s="2" t="n">
         <v>46126.34389560185</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>A few days ago I shared data on which banks UAE SMEs in our portfolio are actually banking with.
 It got significant traction. People were genuinely surprised to see Wio Bank at 18% share. That is a structural shift in how SMEs choose their banking relationships.
@@ -2717,108 +3766,108 @@
 #omnispayInsights #SMEBanking #UAE #Fintech #Payments</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E29" t="n">
         <v>10</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F29" t="n">
         <v>6</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/simantadas1_omnispayinsights-smebanking-uae-activity-7449671578755211264-xWOJ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/simantadas1_omnispayinsights-smebanking-uae-activity-7449671578755211264-xWOJ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>urn:li:activity:7449671578755211264</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>a few days ago i shared data on which banks uae smes in our portfolio are actually banking with. it got significant traction. people were genuinely surprised to see wio bank at 18% share. that is a structural shift in how smes choose their banking relationships. but the question raised was: are digital banks winning share by taking the lower end of the sme segment? are they being lax about who they onboard? that question deserved a proper answer, not an opinion. so i went back to the data. i used tpv (total processed volume) per merchant as a quality proxy. more volume per merchant means a more commercially active business. expressed everything as a multiple of the portfolio average so no raw numbers needed. the answer is in the chart. rakbank stands out. smallest major share at 12.3%, but the highest quality score in the portfolio at 1.75x. emirates nbd and emirates islamic also sit above the line, both running quality multiples well above average despite holding modest share positions. then there is wio bank. 18.3% of merchants. 1.09x quality multiple. above the portfolio average. the hypothesis that digital banks are capturing the lower end of the sme segment does not hold here. wio has managed to scale rapidly and maintain quality simultaneously. they have not traded one for the other. the market share leader and the quality leader are not the same bank. that is worth sitting with. the banks that win both races will define uae sme banking. we are starting to see who they are. #omnispayinsights #smebanking #uae #fintech #payments</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Simanta Das</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>a few days ago i shared data on which banks uae smes in our portfolio are actually banking with. it got significant traction. people were genuinely surprised to see wio bank at 18% share. that is a structural shift in how smes choose their banking relationships. but the question raised was: are digital banks winning share by taking the lower end of the sme segment? are they being lax about who they onboard? that question deserved a proper answer, not an opinion. so i went back to the data. i used tpv (total processed volume) per merchant as a quality proxy. more volume per merchant means a more commercially active business. expressed everything as a multiple of the portfolio average so no raw numbers needed. the answer is in the chart. rakbank stands out. smallest major share at 12.3%, but the highest quality score in the portfolio at 1.75x. emirates nbd and emirates islamic also sit above the line, both running quality multiples well above average despite holding modest share positions. then there is wio bank. 18.3% of merchants. 1.09x quality multiple. above the portfolio average. the hypothesis that digital banks are capturing the lower end of the sme segment does not hold here. wio has managed to scale rapidly and maintain quality simultaneously. they have not traded one for the other. the market share leader and the quality leader are not the same bank. that is worth sitting with. the banks that win both races will define uae sme banking. we are starting to see who they are. #omnispayinsights #smebanking #uae #fintech #payments</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>19</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Wio Bank holds 18.3% market share with a 1.09x quality multiple. • Rakbank has the highest quality score at 1.75x despite a 12.3% share. • Digital banks are not solely capturing the lower end of the SME segment.</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="R29" t="n">
+        <v>28</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>emirates nbd and emirates islamic also sit above the line, both running quality multiples well above average despite holding modest share positions. • smallest major share at 12.3%, but the highest quality score in the portfolio at 1.75x. • but the question raised was: are digital banks winning share by taking the lower end of the sme segment?</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Kamugisha Abel</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C30" s="2" t="n">
         <v>46126.33104324074</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>DP World 
 Alessia Falone-
@@ -2863,108 +3912,108 @@
 Jeebly LLC</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/kamugisha-abel-154055291_resume-activity-7449666921215692800-ziI_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/kamugisha-abel-154055291_resume-activity-7449666921215692800-ziI_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>urn:li:activity:7449666921215692800</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>dp world alessia falone- landmark properties, inc. emirates nbd transguard group group dulsco group llc g4s uae emirates transport arasco logistics rsa security global hellmann worldwide logistics worldwide logistics kuehne+nagel + nagel uae dhl supply chain uae fedex express uae ups healthcare uae takween aldar shirawi group aramex galadari brothers brothers sharaf dg group al majid group takween aldar ghurair group lootah perfumes group emirates group (dnata) gulf agency company (gac) tristar group group milaha logistics majid al futtaim baik logistics union coop lulu retail choithrams spinneys uae carrefour uae nesto group westcon-comstor zone supermarket e-aswaaq llc alo maya group kibsons international llc international emirates post group zajel_official courier services shipa delivery jeebly llc</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Kamugisha Abel</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>dp world alessia falone- landmark properties, inc. emirates nbd transguard group group dulsco group llc g4s uae emirates transport arasco logistics rsa security global hellmann worldwide logistics worldwide logistics kuehne+nagel + nagel uae dhl supply chain uae fedex express uae ups healthcare uae takween aldar shirawi group aramex galadari brothers brothers sharaf dg group al majid group takween aldar ghurair group lootah perfumes group emirates group (dnata) gulf agency company (gac) tristar group group milaha logistics majid al futtaim baik logistics union coop lulu retail choithrams spinneys uae carrefour uae nesto group westcon-comstor zone supermarket e-aswaaq llc alo maya group kibsons international llc international emirates post group zajel_official courier services shipa delivery jeebly llc</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>20</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Numerous logistics and retail companies listed, including DP World and Emirates NBD. • Highlights collaboration among major UAE businesses in logistics and supply chain sectors. • Emphasis on diverse service providers, from courier services to retail chains.</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
+      <c r="R30" t="n">
+        <v>29</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>dp world alessia falone- landmark properties, inc.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B22" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Keith Rawlings Brown</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C31" s="2" t="n">
         <v>46126.16128627315</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>43 days ago physical strikes took down 2 of 3 AWS availability zones in 
 the UAE simultaneously. Multi-AZ deployment failed. Not because the 
@@ -2981,108 +4030,108 @@
 #AWS #CloudResilience #DevOps #SRE #FinOps SpotInstances CloudInfrastructure AWSOutage</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>linkedinVideo</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/keithrawlingsbrown_aws-cloudresilience-devops-activity-7449605403350478849-_QRL?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/keithrawlingsbrown_aws-cloudresilience-devops-activity-7449605403350478849-_QRL?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>urn:li:activity:7449605403350478849</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>43 days ago physical strikes took down 2 of 3 aws availability zones in the uae simultaneously. multi-az deployment failed. not because the architecture was wrong. because two buildings in the same region got hit at the same time. the engineering teams responsible for careem, emirates nbd, and alaan did not make bad decisions. the threat model changed without warning. i have been tracking what the spot market signal looked like before the first strike. the suppression rate in me-central-1 was already diverging from baseline 48 hours before the news broke. that gap is what i am building refinex to close. full suppression log is public: refinex.io/transparency have you had to rebuild a dr plan mid-conflict? #aws #cloudresilience #devops #sre #finops spotinstances cloudinfrastructure awsoutage</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Keith Rawlings Brown</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>43 days ago physical strikes took down 2 of 3 aws availability zones in the uae simultaneously. multi-az deployment failed. not because the architecture was wrong. because two buildings in the same region got hit at the same time. the engineering teams responsible for careem, emirates nbd, and alaan did not make bad decisions. the threat model changed without warning. i have been tracking what the spot market signal looked like before the first strike. the suppression rate in me-central-1 was already diverging from baseline 48 hours before the news broke. that gap is what i am building refinex to close. full suppression log is public: refinex.io/transparency have you had to rebuild a dr plan mid-conflict? #aws #cloudresilience #devops #sre #finops spotinstances cloudinfrastructure awsoutage</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>21</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>43 days ago, physical strikes affected 2 of 3 AWS availability zones in UAE. • Multi-AZ deployment failure was due to simultaneous building strikes, not architectural issues. • Spot market suppression rate diverged from baseline 48 hours before the first strike.</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
+      <c r="R31" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>43 days ago physical strikes took down 2 of 3 aws availability zones in the uae simultaneously. • the suppression rate in me-central-1 was already diverging from baseline 48 hours before the news broke. • full suppression log is public: refinex.io/transparency have you had to rebuild a dr plan mid-conflict?</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Kerolos Sameh</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C32" s="2" t="n">
         <v>46126.0511709375</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Banker's loan 
 The best rate in the market
@@ -3130,108 +4179,108 @@
 Kuwait Finance House Bank Egypt</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>25</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/kerolos-sameh-227a18215_bankers-loan-the-best-rate-in-the-market-activity-7449565498888892416-P8Ip?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADq6p-kBcdJAYJMzAN8VuZZFUmNBfOSttAI</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/kerolos-sameh-227a18215_bankers-loan-the-best-rate-in-the-market-activity-7449565498888892416-P8Ip?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>urn:li:activity:7449565498888892416</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>banker's loan the best rate in the market max loan amount: 8,000,000 max tenor: 120 months rate : 18.5% decreasing available monthly and yearly installments or monthly installments only contact .. kerolos sameh 01097086029 national bank of egypt (nbe) attijariwafa bank egypt alexbank eg bank first abu dhabi bank (fab) midbank banque misr banque du caire cib egypt mashreq ahli united bank abu dhabi islamic bank - egypt abu dhabi commercial bank emirates nbd arab bank bank nxt saib arab african international bank crédit agricole egypt bank abc national bank of kuwait hsbc the united bank of egypt qnb egypt arab international bank al ahli bank of kuwait - egypt بنك البركة مصر بنك التعمير والإسكان hd bank industrial development bank - idb faisal islamic bank of egypt african export-import bank (afreximbank) agricultural bank of egypt central bank of egypt kuwait finance house bank egypt</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Kerolos Sameh</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>banker's loan the best rate in the market max loan amount: 8,000,000 max tenor: 120 months rate : 18.5% decreasing available monthly and yearly installments or monthly installments only contact .. kerolos sameh 01097086029 national bank of egypt (nbe) attijariwafa bank egypt alexbank eg bank first abu dhabi bank (fab) midbank banque misr banque du caire cib egypt mashreq ahli united bank abu dhabi islamic bank - egypt abu dhabi commercial bank emirates nbd arab bank bank nxt saib arab african international bank crédit agricole egypt bank abc national bank of kuwait hsbc the united bank of egypt qnb egypt arab international bank al ahli bank of kuwait - egypt بنك البركة مصر بنك التعمير والإسكان hd bank industrial development bank - idb faisal islamic bank of egypt african export-import bank (afreximbank) agricultural bank of egypt central bank of egypt kuwait finance house bank egypt</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>22</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Maximum loan amount: 8,000,000 EGP with a 120-month tenor. • Interest rate: 18.5% decreasing, with monthly or yearly installments available. • Contact: Kerolos Sameh at 01097086029 for more information.</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
+      <c r="R32" t="n">
+        <v>31</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>banker's loan the best rate in the market max loan amount: 8,000,000 max tenor: 120 months rate : 18.5% decreasing available monthly and yearly installments or monthly installments only contact ..</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>PARTHA SARATHY</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C33" s="2" t="n">
         <v>46125.6336645949</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Reflecting on a monumental year for Indian Finance: A wrap-up of FY26! 🇮🇳🏦
 ​As we look back at the financial year gone by, it’s clear that the landscape of Indian banking and macroeconomics has undergone a massive transformation. From major global stake acquisitions to regulatory overhauls, the "Banker’s Trust" by Tamal Bandyopadhyay highlights a rollercoaster year.
@@ -3258,108 +4307,108 @@
  #FY26 #RBI #FinanceNews #InvestmentBanking #PrivateEquity #StockMarketIndia #Macroeconomics #HDFCBank #YesBank #FederalBank #ShriramFinance #GlobalFinance</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E33" t="n">
         <v>2</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/partha-sarathy-7309391ab_banking-indianeconomy-fy26-activity-7449414199656513536-Ox8I?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/partha-sarathy-7309391ab_banking-indianeconomy-fy26-activity-7449414199656513536-Ox8I?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>urn:li:activity:7449414199656513536</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>reflecting on a monumental year for indian finance: a wrap-up of fy26! ​as we look back at the financial year gone by, it’s clear that the landscape of indian banking and macroeconomics has undergone a massive transformation. from major global stake acquisitions to regulatory overhauls, the "banker’s trust" by tamal bandyopadhyay highlights a rollercoaster year. ​here are the defining trends of fy25-26: ​ macro indicators: a mixed bag ​the rupee: depreciated from ₹85.51 to ₹94.83 against the dollar over the year. ​forex reserves: a silver lining, rising from $676.3b to $697.1b. ​interest rates: the rbi was proactive, cutting the policy repo rate by 1.25 percentage points to 5.25%. ​market performance: while nifty and sensex saw their weakest performance in six years, the mutual fund industry bucked the trend, growing its aum by over 20%. ​ the foreign play: global giants move in ​fy26 was the year foreign capital truly "played" in the indian banking turf: ​blackstone acquired nearly 10% in federal bank. ​warburg pincus &amp; adia pumped ₹7,500 crore into idfc first bank. ​emirates nbd received the nod to acquire a majority stake (up to 74%) in rbl bank, a move that could turn it into a subsidiary of the dubai-based lender. ​sumitomo mitsui (smbc) became the largest shareholder in yes bank with a 24.9% stake. ​mufg bank (japan) made a landmark move on the nbfc front, acquiring 20% of shriram finance for nearly ₹40,000 crore. ​ regulatory evolution ​the rbi wasn't just watching; it was busy simplifying. close to 9,000 circulars were consolidated into just 238 master directions. this shift toward "anticipatory supervision" rather than "reactive rule-making" is a game-changer for governance in the sector. ​ corporate governance &amp; the unfinished agenda ​the year wasn't without its drama. the sudden resignation of hdfc bank’s non-executive chairman, atanu chakraborty, citing "personal values and ethics," has left analysts searching for answers despite a clean chit from the regulator. meanwhile, the long-awaited privatization of idbi bank remains the "big event" that is yet to cross the finish line. ​what was the most significant financial event of fy26 for you? whether it's the interest rate cuts or the entry of global pe giants, the indian financial story is becoming more global than ever. ​#banking #indianeconomy #fy26 #rbi #financenews #investmentbanking #privateequity #stockmarketindia #macroeconomics #hdfcbank #yesbank #federalbank #shriramfinance #globalfinance</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>PARTHA SARATHY</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>reflecting on a monumental year for indian finance: a wrap-up of fy26! ​as we look back at the financial year gone by, it’s clear that the landscape of indian banking and macroeconomics has undergone a massive transformation. from major global stake acquisitions to regulatory overhauls, the "banker’s trust" by tamal bandyopadhyay highlights a rollercoaster year. ​here are the defining trends of fy25-26: ​ macro indicators: a mixed bag ​the rupee: depreciated from ₹85.51 to ₹94.83 against the dollar over the year. ​forex reserves: a silver lining, rising from $676.3b to $697.1b. ​interest rates: the rbi was proactive, cutting the policy repo rate by 1.25 percentage points to 5.25%. ​market performance: while nifty and sensex saw their weakest performance in six years, the mutual fund industry bucked the trend, growing its aum by over 20%. ​ the foreign play: global giants move in ​fy26 was the year foreign capital truly "played" in the indian banking turf: ​blackstone acquired nearly 10% in federal bank. ​warburg pincus &amp; adia pumped ₹7,500 crore into idfc first bank. ​emirates nbd received the nod to acquire a majority stake (up to 74%) in rbl bank, a move that could turn it into a subsidiary of the dubai-based lender. ​sumitomo mitsui (smbc) became the largest shareholder in yes bank with a 24.9% stake. ​mufg bank (japan) made a landmark move on the nbfc front, acquiring 20% of shriram finance for nearly ₹40,000 crore. ​ regulatory evolution ​the rbi wasn't just watching; it was busy simplifying. close to 9,000 circulars were consolidated into just 238 master directions. this shift toward "anticipatory supervision" rather than "reactive rule-making" is a game-changer for governance in the sector. ​ corporate governance &amp; the unfinished agenda ​the year wasn't without its drama. the sudden resignation of hdfc bank’s non-executive chairman, atanu chakraborty, citing "personal values and ethics," has left analysts searching for answers despite a clean chit from the regulator. meanwhile, the long-awaited privatization of idbi bank remains the "big event" that is yet to cross the finish line. ​what was the most significant financial event of fy26 for you? whether it's the interest rate cuts or the entry of global pe giants, the indian financial story is becoming more global than ever. ​#banking #indianeconomy #fy26 #rbi #financenews #investmentbanking #privateequity #stockmarketindia #macroeconomics #hdfcbank #yesbank #federalbank #shriramfinance #globalfinance</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>23</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>The rupee depreciated from ₹85.51 to ₹94.83 against the dollar in FY26. • Blackstone acquired nearly 10% in Federal Bank during FY26. • RBI consolidated 9,000 circulars into 238 master directions for better governance.</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
+      <c r="R33" t="n">
+        <v>32</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>​ the foreign play: global giants move in ​fy26 was the year foreign capital truly "played" in the indian banking turf: ​blackstone acquired nearly 10% in federal bank. • ​mufg bank (japan) made a landmark move on the nbfc front, acquiring 20% of shriram finance for nearly ₹40,000 crore. • ​here are the defining trends of fy25-26: ​ macro indicators: a mixed bag ​the rupee: depreciated from ₹85.51 to ₹94.83 against the dollar over the year.</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>Arab Elite Leaders</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C34" s="2" t="n">
         <v>46125.60968489583</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>🌟 Elite Leader Spotlight | 
 تسليط الضوء على القيادات العربية
@@ -3381,112 +4430,112 @@
 it is about shaping organizations by placing the right people where impact truly happens.”</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E34" t="n">
         <v>48</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/arabeliteleaders_elite-leader-spotlight-%D8%AA%D8%B3%D9%84%D9%8A%D8%B7-%D8%A7%D9%84%D8%B6%D9%88%D8%A1-activity-7449405509704736768-3Bhe?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/arabeliteleaders_elite-leader-spotlight-%D8%AA%D8%B3%D9%84%D9%8A%D8%B7-%D8%A7%D9%84%D8%B6%D9%88%D8%A1-activity-7449405509704736768-3Bhe?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>urn:li:activity:7449405509704736768</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>elite leader spotlight | تسليط الضوء على القيادات العربية رند الداود — متخصصة استقطاب المواهب والتوظيف rand aldawood cipd l5 talent acquisition &amp; recruitment expert الهيئة العامة للطيران المدني | gaca الرياض، المملكة العربية السعودية حاصلة على cipd level 5 في إدارة الأفراد، رند تقود جهود استقطاب الكفاءات النوعية والقيادات المتخصصة في إحدى أبرز الجهات الحكومية بالمملكة. تؤمن رند بأن استقطاب المواهب لا يقتصر على شغل الوظائف — بل هو بناء مؤسسات قوية بوضع الكفاءات المناسبة في المواقع التي تصنع الأثر الحقيقي. أبرز إنجازاتها: ريادة تطبيق حلول التوظيف المدعومة بالذكاء الاصطناعي استقطاب الكفاءات المتوافقة مع أولويات رؤية 2030 خبرة متنوعة: hsbc السعودية · emirates nbd · sambacapital “talent acquisition is not just about filling roles it is about shaping organizations by placing the right people where impact truly happens.”</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Arab Elite Leaders</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>elite leader spotlight | تسليط الضوء على القيادات العربية رند الداود — متخصصة استقطاب المواهب والتوظيف rand aldawood cipd l5 talent acquisition &amp; recruitment expert الهيئة العامة للطيران المدني | gaca الرياض، المملكة العربية السعودية حاصلة على cipd level 5 في إدارة الأفراد، رند تقود جهود استقطاب الكفاءات النوعية والقيادات المتخصصة في إحدى أبرز الجهات الحكومية بالمملكة. تؤمن رند بأن استقطاب المواهب لا يقتصر على شغل الوظائف — بل هو بناء مؤسسات قوية بوضع الكفاءات المناسبة في المواقع التي تصنع الأثر الحقيقي. أبرز إنجازاتها: ريادة تطبيق حلول التوظيف المدعومة بالذكاء الاصطناعي استقطاب الكفاءات المتوافقة مع أولويات رؤية 2030 خبرة متنوعة: hsbc السعودية · emirates nbd · sambacapital “talent acquisition is not just about filling roles it is about shaping organizations by placing the right people where impact truly happens.”</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>24</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Rand Al-Dawood specializes in talent acquisition and recruitment at GACA, Saudi Arabia. • Achieved CIPD Level 5 in Human Resource Management. • Led AI-supported recruitment solutions aligned with Vision 2030 priorities.</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
+      <c r="R34" t="n">
+        <v>33</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>تؤمن رند بأن استقطاب المواهب لا يقتصر على شغل الوظائف — بل هو بناء مؤسسات قوية بوضع الكفاءات المناسبة في المواقع التي تصنع الأثر الحقيقي.</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Peter Barr</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C35" s="2" t="n">
         <v>46125.56342947917</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>UAE Markets Weekly Update | Week 15: Apr 6 - Apr 10, 2026
 The Iran ceasefire saw a sharp market reversal last week. UAE markets bounced hard alongside global equities, the DFM General Index surged +4.20% and the FTSE ADX gained +2.48%, with the MSCI UAE up +5.64%. The recent holding pattern broke decisively to the upside, though the multi-timeframe trend picture remains cautious.
@@ -3500,108 +4549,108 @@
 #UAE #DFM #ADX #Stocks #Dubai #AbuDhabi</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E35" t="n">
         <v>7</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/peterbarrdubai_uae-weekly-market-update-activity-7449388747302907904-p29i?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/peterbarrdubai_uae-weekly-market-update-activity-7449388747302907904-p29i?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>urn:li:activity:7449388747302907904</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>uae markets weekly update | week 15: apr 6 - apr 10, 2026 the iran ceasefire saw a sharp market reversal last week. uae markets bounced hard alongside global equities, the dfm general index surged +4.20% and the ftse adx gained +2.48%, with the msci uae up +5.64%. the recent holding pattern broke decisively to the upside, though the multi-timeframe trend picture remains cautious. 80 stocks positive vs 14 negative; average weekly return +3.06% strong performers: air arabia (+17.0%), salik (+9.9%), emirates nbd (+8.8%), parkin (+8.7%), emaar development (+6.2%) volume conviction returned: dfm volume surged +60.9% to 1,224.7m; adx up +5.3% to 980.7m breadth remains structurally weak despite the rally: daily net bullish at -59, weekly at -21; 13.6% of msci uae constituents at 250-day lows, 0% making new highs there was a damaging wave of new lows during the week, prior to the ceasefire: islamic arab insurance, burjeel holdings, space42, al firdous holdings, and abu dhabi national energy all hit all-time lows — no positive breakouts recorded highest-ranked stocks on trend scoring: amlak finance, dubai investments, fertiglobe, borouge, air arabia for informational purposes only. source: aporia analytics #uae #dfm #adx #stocks #dubai #abudhabi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Peter Barr</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>uae markets weekly update | week 15: apr 6 - apr 10, 2026 the iran ceasefire saw a sharp market reversal last week. uae markets bounced hard alongside global equities, the dfm general index surged +4.20% and the ftse adx gained +2.48%, with the msci uae up +5.64%. the recent holding pattern broke decisively to the upside, though the multi-timeframe trend picture remains cautious. 80 stocks positive vs 14 negative; average weekly return +3.06% strong performers: air arabia (+17.0%), salik (+9.9%), emirates nbd (+8.8%), parkin (+8.7%), emaar development (+6.2%) volume conviction returned: dfm volume surged +60.9% to 1,224.7m; adx up +5.3% to 980.7m breadth remains structurally weak despite the rally: daily net bullish at -59, weekly at -21; 13.6% of msci uae constituents at 250-day lows, 0% making new highs there was a damaging wave of new lows during the week, prior to the ceasefire: islamic arab insurance, burjeel holdings, space42, al firdous holdings, and abu dhabi national energy all hit all-time lows — no positive breakouts recorded highest-ranked stocks on trend scoring: amlak finance, dubai investments, fertiglobe, borouge, air arabia for informational purposes only. source: aporia analytics #uae #dfm #adx #stocks #dubai #abudhabi</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>25</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>DFM General Index surged +4.20% and FTSE ADX gained +2.48% last week. • 80 stocks were positive, with Air Arabia up +17.0%. • 13.6% of MSCI UAE constituents hit 250-day lows, indicating weak breadth.</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
+      <c r="R35" t="n">
+        <v>34</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>uae markets bounced hard alongside global equities, the dfm general index surged +4.20% and the ftse adx gained +2.48%, with the msci uae up +5.64%. • uae markets weekly update | week 15: apr 6 - apr 10, 2026 the iran ceasefire saw a sharp market reversal last week. • source: aporia analytics #uae #dfm #adx #stocks #dubai #abudhabi</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B27" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Oliver Lucas</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C36" s="2" t="n">
         <v>46125.55604289352</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Want to Increase Your Sales?
 We provide fresh and high-quality leads for:
@@ -3616,326 +4665,326 @@
 #gulfleads #gulfcreditsolutions #DSAUAE #loansales #bankingleads #UAEFinance #Leadgeneration #leads Mashreq Mashreq NEO Emirates NBD Emirates Islamic First Abu Dhabi Bank (FAB) Abu Dhabi Commercial Bank ADIB - Abu Dhabi Islamic Bank RAKBANK</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/oliver-lucas-523177369_gulfleads-gulfcreditsolutions-dsauae-activity-7449386070493974528-hhDz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/oliver-lucas-523177369_gulfleads-gulfcreditsolutions-dsauae-activity-7449386070493974528-hhDz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>urn:li:activity:7449386070493974528</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>want to increase your sales? we provide fresh and high-quality leads for: credit cards business loans personal loans high conversion potential updated database perfect for sales agents &amp; teams turn leads into approvals today! contact now: +971-562672909 #gulfleads #gulfcreditsolutions #dsauae #loansales #bankingleads #uaefinance #leadgeneration #leads mashreq mashreq neo emirates nbd emirates islamic first abu dhabi bank (fab) abu dhabi commercial bank adib - abu dhabi islamic bank rakbank</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Oliver Lucas</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>want to increase your sales? we provide fresh and high-quality leads for: credit cards business loans personal loans high conversion potential updated database perfect for sales agents &amp; teams turn leads into approvals today! contact now: +971-562672909 #gulfleads #gulfcreditsolutions #dsauae #loansales #bankingleads #uaefinance #leadgeneration #leads mashreq mashreq neo emirates nbd emirates islamic first abu dhabi bank (fab) abu dhabi commercial bank adib - abu dhabi islamic bank rakbank</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>26</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Fresh, high-quality leads for credit cards and loans available. • Updated database ideal for sales agents and teams. • Contact for lead generation at +971-562672909.</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
+      <c r="R36" t="n">
+        <v>35</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>we provide fresh and high-quality leads for: credit cards business loans personal loans high conversion potential updated database perfect for sales agents &amp; teams turn leads into approvals today! • want to increase your sales?</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Wonderful Lending Mortgage Broker</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C37" s="2" t="n">
         <v>46125.50624409723</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Expert Guidance to Secure Your Ideal Mortgage
 Wonder Lending is a premier Dubai-based mortgage consultancy firm specializing in home finance solutions across the United Arab Emirates. We act as an independent mortgage broker, offering direct access to mortgage products from all major UAE banks, including Emirates NBD, ADCB, Mashreq, FAB, ADIB, DIB, and more.
 #wonderlending #mortgage #dubai #realestate</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/wonder-lending-mortgage-broker_wonderlending-mortgage-dubai-activity-7449368024014462976-cZ1X?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/wonder-lending-mortgage-broker_wonderlending-mortgage-dubai-activity-7449368024014462976-cZ1X?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>urn:li:activity:7449368024014462976</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>expert guidance to secure your ideal mortgage wonder lending is a premier dubai-based mortgage consultancy firm specializing in home finance solutions across the united arab emirates. we act as an independent mortgage broker, offering direct access to mortgage products from all major uae banks, including emirates nbd, adcb, mashreq, fab, adib, dib, and more. #wonderlending #mortgage #dubai #realestate</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Wonderful Lending Mortgage Broker</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>expert guidance to secure your ideal mortgage wonder lending is a premier dubai-based mortgage consultancy firm specializing in home finance solutions across the united arab emirates. we act as an independent mortgage broker, offering direct access to mortgage products from all major uae banks, including emirates nbd, adcb, mashreq, fab, adib, dib, and more. #wonderlending #mortgage #dubai #realestate</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>27</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Wonder Lending is a Dubai-based mortgage consultancy firm. • Offers access to mortgage products from major UAE banks. • Specializes in home finance solutions across the UAE.</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
+      <c r="R37" t="n">
+        <v>36</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>expert guidance to secure your ideal mortgage wonder lending is a premier dubai-based mortgage consultancy firm specializing in home finance solutions across the united arab emirates. • we act as an independent mortgage broker, offering direct access to mortgage products from all major uae banks, including emirates nbd, adcb, mashreq, fab, adib, dib, and more. • #wonderlending #mortgage #dubai #realestate</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Hammad Azam</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C38" s="2" t="n">
         <v>46125.49101383102</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>This strategic move by Sobha and Emirates NBD will help investors achieve their investment goals.</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E38" t="n">
         <v>1</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/hammad-thedubaidealmaker_sobharealty-emiratesnbd-strategicpartnership-activity-7449362504750710784--2rZ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/hammad-thedubaidealmaker_sobharealty-emiratesnbd-strategicpartnership-activity-7449362504750710784--2rZ?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>urn:li:activity:7449362504750710784</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>this strategic move by sobha and emirates nbd will help investors achieve their investment goals.</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Hammad Azam</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>this strategic move by sobha and emirates nbd will help investors achieve their investment goals.</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>28</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Sobha and Emirates NBD collaborate for investor support. • Strategic move aims to enhance investment goals.</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
+      <c r="R38" t="n">
+        <v>37</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>this strategic move by sobha and emirates nbd will help investors achieve their investment goals.</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>Farhan Shaikh</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C39" s="2" t="n">
         <v>46125.48386877315</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Every journey starts with a direction.
 Working in Business Banking at Emirates NBD has given me the opportunity to connect with professionals, entrepreneurs, and businesses across the UAE.
@@ -3945,1051 +4994,6 @@
 #Networking #DubaiBusiness #EmiratesNBD #BusinessBanking #Growth #UAE</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/farhan-shaikh-56b9b5117_networking-dubaibusiness-emiratesnbd-activity-7449359915468529664-X36W?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAE4W700Ba2ZH3TT3WFNdtt_cuNQs1kG3prE</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449359915468529664</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>every journey starts with a direction. working in business banking at emirates nbd has given me the opportunity to connect with professionals, entrepreneurs, and businesses across the uae. in a fast-moving environment like dubai, building the right connections and understanding client needs makes all the difference. always open to connecting with business owners, consultants, and professionals who may require support with banking solutions. let’s connect and grow together. #networking #dubaibusiness #emiratesnbd #businessbanking #growth #uae</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Farhan Shaikh</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>every journey starts with a direction. working in business banking at emirates nbd has given me the opportunity to connect with professionals, entrepreneurs, and businesses across the uae. in a fast-moving environment like dubai, building the right connections and understanding client needs makes all the difference. always open to connecting with business owners, consultants, and professionals who may require support with banking solutions. let’s connect and grow together. #networking #dubaibusiness #emiratesnbd #businessbanking #growth #uae</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
-        <v>29</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Working in business banking at Emirates NBD connects me with UAE professionals and businesses. • Emphasizes the importance of building connections and understanding client needs in Dubai. • Open to networking with business owners and consultants for banking support.</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Banky Egypt</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>46125.92028388889</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>📌يعزز #Apple_Pay 📲 تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر
-للتفاصيل👈 https://lnkd.in/dDFennux
-#بنكي
-‏Emirates NBD</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>219,364</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/banky-egypt_appleabrpay-aeqaeuaerabraepaesaenaetaepaezaepaesabraexaeqaeyabraepaesaewaefaeuaey-activity-7449518067010760705-YEmT?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449518067010760705</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>يعزز #apple_pay تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر للتفاصيل  #بنكي ‏emirates nbd</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Banky Egypt</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>يعزز #apple_pay تجربة المدفوعات لعملاء #بنك_الإمارات_دبي_الوطني مصر للتفاصيل  #بنكي ‏emirates nbd</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
-        <v>30</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Apple Pay enhances payment experience for Emirates NBD customers in Egypt. • Collaboration focuses on improving digital payment solutions.</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Mohammad Nadeem</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>46125.91631365741</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Grateful to receive this appreciation for my contribution to our DX Engineering Practices.
-This journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. It took a lot of deep dives, iterations, and persistence, but absolutely worth it.
-A big thank you to my manager, leadership, and the entire team for the support and trust throughout.
-Looking forward to building more and pushing boundaries! 
-Emirates NBD  Miguel Rio-Tinto  Ahmad Kayyali Speridian UAE  Speridian Technologies 
-#Gratitude #TeamWork #Engineering #ContinuousLearning</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>22</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ndm-0501_gratitude-teamwork-engineering-activity-7449516628246949888-X0hs?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449516628246949888</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>grateful to receive this appreciation for my contribution to our dx engineering practices. this journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. it took a lot of deep dives, iterations, and persistence, but absolutely worth it. a big thank you to my manager, leadership, and the entire team for the support and trust throughout. looking forward to building more and pushing boundaries! emirates nbd miguel rio-tinto ahmad kayyali speridian uae speridian technologies #gratitude #teamwork #engineering #continuouslearning</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Mohammad Nadeem</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>grateful to receive this appreciation for my contribution to our dx engineering practices. this journey was all about solving real problems, improving data-driven capabilities, and building something impactful for the team. it took a lot of deep dives, iterations, and persistence, but absolutely worth it. a big thank you to my manager, leadership, and the entire team for the support and trust throughout. looking forward to building more and pushing boundaries! emirates nbd miguel rio-tinto ahmad kayyali speridian uae speridian technologies #gratitude #teamwork #engineering #continuouslearning</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R32" t="n">
-        <v>31</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Received appreciation for contributions to DX engineering practices. • Focused on solving real problems and improving data-driven capabilities. • Acknowledged support from manager and team throughout the journey.</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Marketics Agency</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>46125.90151929398</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Quelle banque recommandez-vous ?
-Prenez le temps de répondre honnêtement.
-Notre analyse du secteur bancaire marocain — et de ce que JPMorgan, Emirates NBD et Bank of America ont compris avant tout le monde — est disponible en document joint.
-Marketics | Agence Marketing &amp; Communication</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/marketics-premiumagency_secteur-bancaire-toutes-les-banques-sont-activity-7449511266949156864-ntuA?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449511266949156864</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>quelle banque recommandez-vous ? prenez le temps de répondre honnêtement. notre analyse du secteur bancaire marocain — et de ce que jpmorgan, emirates nbd et bank of america ont compris avant tout le monde — est disponible en document joint. marketics | agence marketing &amp; communication</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Marketics Agency</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>quelle banque recommandez-vous ? prenez le temps de répondre honnêtement. notre analyse du secteur bancaire marocain — et de ce que jpmorgan, emirates nbd et bank of america ont compris avant tout le monde — est disponible en document joint. marketics | agence marketing &amp; communication</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>32</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Analysis of the Moroccan banking sector available in the attached document. • Insights from JPMorgan, Emirates NBD, and Bank of America included. • Request for honest recommendations on banks.</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Aswila Sood</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>46125.8570941088</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>I am pleased to have completed the One Million Prompters program, initiative by the Dubai Future Foundation and the Dubai Centre for Artificial Intelligence.
-I extend my sincere gratitude to His Highness Sheikh Hamdan bin Mohammed bin Rashid Al Maktoum for this opportunity, and to Emirates NBD for their support.
-This certification has strengthened my skills in generative AI and prompt engineering, preparing me for an AI-driven future.
-#OneMillionPrompters #AI #GenerativeAI #FutureSkills #Dubai
-#LearningAndDevelopment#EmiratesNBD</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>12</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/aswila-sood-0758539b_onemillionprompters-ai-generativeai-activity-7449495167801389056-jXWi?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449495167801389056</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>i am pleased to have completed the one million prompters program, initiative by the dubai future foundation and the dubai centre for artificial intelligence. i extend my sincere gratitude to his highness sheikh hamdan bin mohammed bin rashid al maktoum for this opportunity, and to emirates nbd for their support. this certification has strengthened my skills in generative ai and prompt engineering, preparing me for an ai-driven future. #onemillionprompters #ai #generativeai #futureskills #dubai #learninganddevelopment#emiratesnbd</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Aswila Sood</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>i am pleased to have completed the one million prompters program, initiative by the dubai future foundation and the dubai centre for artificial intelligence. i extend my sincere gratitude to his highness sheikh hamdan bin mohammed bin rashid al maktoum for this opportunity, and to emirates nbd for their support. this certification has strengthened my skills in generative ai and prompt engineering, preparing me for an ai-driven future. #onemillionprompters #ai #generativeai #futureskills #dubai #learninganddevelopment#emiratesnbd</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>33</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Completed the One Million Prompters program by Dubai Future Foundation. • Certification enhanced skills in generative AI and prompt engineering. • Acknowledged support from His Highness Sheikh Hamdan and Emirates NBD.</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Brunella Lupano</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>46125.84993825232</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>As of April 2026, the #UAE's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. This total is heavily anchored by the International Holding Company LLC (#IHC), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value. 
-Top 10 #UAE Companies by Market Capitalization (2026)
-Based on the Forbes Middle East 2026 ranking, the most valuable publicly listed companies in the UAE are:
-International Holding Company LLC (IHC): $238.6 billion
-TAQA Group (Abu Dhabi National Energy Company): $87.9 billion
-ADNOC Group: $75.4 billion
-First Abu Dhabi Bank (FAB): $56.0 billion
-Emirates NBD Group: $53.5 billion
-e&amp; UAE (formerly etisalat Group): $46.7 billion
-Dubai Electricity &amp; Water Authority - DEWA: $41.1 billion
-Emaar Dubai Properties: $36.1 billion
-Abu Dhabi Commercial Bank (ADCB)
-Alpha Dhabi Holding (ADH) 
-Market Composition and Key #Trends
-&gt; Sector Dominance: The #Banking and #Financial #Services sector remains the most represented, featuring major players like FAB, Emirates NBD, and ADCB.
-&gt; Regional Context: The UAE leads the region in the number of companies on the "Top 100 Most Valuable" list with 35 entries, slightly ahead of Saudi Arabia's 34.
-&gt; #Energy and Utility Weight: Despite having fewer companies than the financial sector, the #Energy sector (including TAQA and ADNOC Gas) commands immense #market #value due to the scale of hydrocarbon and utility operations.
-&gt; Exchange #Resilience: Market gains in early 2026 were supported by a 6.4% rise in the Dubai Financial Market (DFM) and a 2.9% gain in the Abu Dhabi Securities Exchange (ADX) during January.</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/brunellalupano_uae-valuable-companies-activity-7449492574605680640-hR0W?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449492574605680640</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>as of april 2026, the #uae's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. this total is heavily anchored by the international holding company llc (#ihc), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value. top 10 #uae companies by market capitalization (2026) based on the forbes middle east 2026 ranking, the most valuable publicly listed companies in the uae are: international holding company llc (ihc): $238.6 billion taqa group (abu dhabi national energy company): $87.9 billion adnoc group: $75.4 billion first abu dhabi bank (fab): $56.0 billion emirates nbd group: $53.5 billion e&amp; uae (formerly etisalat group): $46.7 billion dubai electricity &amp; water authority - dewa: $41.1 billion emaar dubai properties: $36.1 billion abu dhabi commercial bank (adcb) alpha dhabi holding (adh) market composition and key #trends &gt; sector dominance: the #banking and #financial #services sector remains the most represented, featuring major players like fab, emirates nbd, and adcb. &gt; regional context: the uae leads the region in the number of companies on the "top 100 most valuable" list with 35 entries, slightly ahead of saudi arabia's 34. &gt; #energy and utility weight: despite having fewer companies than the financial sector, the #energy sector (including taqa and adnoc gas) commands immense #market #value due to the scale of hydrocarbon and utility operations. &gt; exchange #resilience: market gains in early 2026 were supported by a 6.4% rise in the dubai financial market (dfm) and a 2.9% gain in the abu dhabi securities exchange (adx) during january.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Brunella Lupano</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>as of april 2026, the #uae's top 10 most #valuable #companies hold a combined market capitalization of $692.3 #billion. this total is heavily anchored by the international holding company llc (#ihc), which alone accounts for over 34% ($238.6 #billion) of the group's aggregate value. top 10 #uae companies by market capitalization (2026) based on the forbes middle east 2026 ranking, the most valuable publicly listed companies in the uae are: international holding company llc (ihc): $238.6 billion taqa group (abu dhabi national energy company): $87.9 billion adnoc group: $75.4 billion first abu dhabi bank (fab): $56.0 billion emirates nbd group: $53.5 billion e&amp; uae (formerly etisalat group): $46.7 billion dubai electricity &amp; water authority - dewa: $41.1 billion emaar dubai properties: $36.1 billion abu dhabi commercial bank (adcb) alpha dhabi holding (adh) market composition and key #trends &gt; sector dominance: the #banking and #financial #services sector remains the most represented, featuring major players like fab, emirates nbd, and adcb. &gt; regional context: the uae leads the region in the number of companies on the "top 100 most valuable" list with 35 entries, slightly ahead of saudi arabia's 34. &gt; #energy and utility weight: despite having fewer companies than the financial sector, the #energy sector (including taqa and adnoc gas) commands immense #market #value due to the scale of hydrocarbon and utility operations. &gt; exchange #resilience: market gains in early 2026 were supported by a 6.4% rise in the dubai financial market (dfm) and a 2.9% gain in the abu dhabi securities exchange (adx) during january.</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>34</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>UAE's top 10 companies have a combined market cap of $692.3 billion as of April 2026. • International Holding Company (IHC) accounts for over 34% of this value at $238.6 billion. • UAE leads the region with 35 companies in the "top 100 most valuable" list.</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>PakBanker</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>46125.77408923611</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>The Central Bank of The UAE has confirmed that its 1 trillion dirham Financial Institutions Resilience Package successfully insulated the economy from regional shocks. Governor Khaled Mohamed Balama and major bank CEOs reported robust growth, with total assets reaching 5.5 trillion dirhams alongside significant progress in digital projects like the Jaywan card scheme and Aani payments. Read more: https://lnkd.in/ddNF9Qvb
-Mustafa Al Khalfawi | National Bank of Umm Al Qaiwain (P.S.C), is Licensed by the Central Bank of the UAE | Emirates NBD | First Abu Dhabi Bank (FAB) | Abu Dhabi Islamic Bank - Egypt | Ajman Bank | Dubai Islamic Bank Pakistan | Mashreq | Abu Dhabi Commercial Bank
-#pakbanker #pakistanbankingnews #banksinpakistan #PAKBANKER #PakBanker #CBUAE #UAEBanking #FinancialResilience #DigitalFinance #Jaywan #AaniPayments #KhaledBalama #Fintech #GlobalFinance #BankingStability #DigitalTransformation #SMEsupport #EconomyUAE #FinancialInfrastructure #SecurityCompliance</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2,153</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/pakbanker_central-bank-of-the-uae-reports-success-in-activity-7449465087842758656-dQqv?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449465087842758656</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>the central bank of the uae has confirmed that its 1 trillion dirham financial institutions resilience package successfully insulated the economy from regional shocks. governor khaled mohamed balama and major bank ceos reported robust growth, with total assets reaching 5.5 trillion dirhams alongside significant progress in digital projects like the jaywan card scheme and aani payments. read more:  mustafa al khalfawi | national bank of umm al qaiwain (p.s.c), is licensed by the central bank of the uae | emirates nbd | first abu dhabi bank (fab) | abu dhabi islamic bank - egypt | ajman bank | dubai islamic bank pakistan | mashreq | abu dhabi commercial bank #pakbanker #pakistanbankingnews #banksinpakistan #pakbanker #pakbanker #cbuae #uaebanking #financialresilience #digitalfinance #jaywan #aanipayments #khaledbalama #fintech #globalfinance #bankingstability #digitaltransformation #smesupport #economyuae #financialinfrastructure #securitycompliance</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>PakBanker</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>the central bank of the uae has confirmed that its 1 trillion dirham financial institutions resilience package successfully insulated the economy from regional shocks. governor khaled mohamed balama and major bank ceos reported robust growth, with total assets reaching 5.5 trillion dirhams alongside significant progress in digital projects like the jaywan card scheme and aani payments. read more:  mustafa al khalfawi | national bank of umm al qaiwain (p.s.c), is licensed by the central bank of the uae | emirates nbd | first abu dhabi bank (fab) | abu dhabi islamic bank - egypt | ajman bank | dubai islamic bank pakistan | mashreq | abu dhabi commercial bank #pakbanker #pakistanbankingnews #banksinpakistan #pakbanker #pakbanker #cbuae #uaebanking #financialresilience #digitalfinance #jaywan #aanipayments #khaledbalama #fintech #globalfinance #bankingstability #digitaltransformation #smesupport #economyuae #financialinfrastructure #securitycompliance</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>35</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>UAE's 1 trillion dirham package insulated economy from regional shocks. • Total bank assets reached 5.5 trillion dirhams. • Significant progress in digital projects like Jaywan card and Aani payments.</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Climena Middle East</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>46125.75018515046</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Title:
-Where ESG Intelligence Meets Shariah-Compliant Digital Finance
-Speakers:
-Fahad Siddiqui - CEO &amp; Founder, Al Mabrook Finance
-Sajjeed Aslam - Partner, Sustainadility LLC USA
-Hina Nasir - Partner, Sustainadility LLC USA
-In this snippet, Fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with Real World Asset (RWA) tokens that are backed by tangible, physical assets.
-He explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas RWA tokens are anchored in real assets such as real estate, commodities, or infrastructure. 
-This fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets.
-Full Session : https://lnkd.in/dWEZyPaX
-Climena Middle East SAJJEED ASLAM Faraz Khan MBE Hina Nasir Kashif (Kash) Aqeel Ahsan Abdullah Khan Fahad Siddiqui Emirates NBD First Abu Dhabi Bank (FAB) Abu Dhabi Commercial Bank Dubai Islamic Bank Pakistan Mashreq Corporate &amp; Investment Banking Group RAKBANK Commercial Bank of Dubai Abu Dhabi Islamic Bank - Egypt Sharjah Islamic Bank Ajman Bank National Bank of Fujairah (NBF) Bank of Sharjah Commercial Bank HSBC Standard Chartered National Bank of Bahrain The Saudi National Bank - SNB</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>linkedinVideo</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/climena-middle-east_title-where-esg-intelligence-meets-shariah-compliant-activity-7449456425292005377-B0hY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449456425292005377</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Climena Middle East</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
-        <v>36</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Fahad Siddiqui contrasts volatile cryptocurrencies with stable real world asset (RWA) tokens. • RWA tokens are backed by tangible assets like real estate and commodities. • The distinction affects stability, risk profiles, and investor perceptions of value.</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sustainadility</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>46125.75000565972</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Title:
-Where ESG Intelligence Meets Shariah-Compliant Digital Finance
-Speakers:
-Fahad Siddiqui - CEO &amp; Founder, Al Mabrook Finance
-Sajjeed Aslam - Partner, Sustainadility LLC USA 
-Hina Nasir - Partner, Sustainadility LLC USA
-In this snippet, Fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with Real World Asset (RWA) tokens that are backed by tangible, physical assets.
-He explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas RWA tokens are anchored in real assets such as real estate, commodities, or infrastructure. 
-This fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets.
-Full Session : https://lnkd.in/dWEZyPaX
-Climena Middle East SAJJEED ASLAM Faraz Khan MBE Hina Nasir Kashif (Kash) Aqeel Ahsan Abdullah Khan Fahad Siddiqui Emirates NBD First Abu Dhabi Bank (FAB) Abu Dhabi Commercial Bank Dubai Islamic Bank Pakistan Mashreq Corporate &amp; Investment Banking Group RAKBANK Commercial Bank of Dubai Abu Dhabi Islamic Bank - Egypt Sharjah Islamic Bank Ajman Bank National Bank of Fujairah (NBF) Bank of Sharjah Commercial Bank HSBC Standard Chartered National Bank of Bahrain The Saudi National Bank - SNB</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>8</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>linkedinVideo</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1,486</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/sustainadility_title-where-esg-intelligence-meets-shariah-compliant-activity-7449456360246722560-R-3z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449456360246722560</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Sustainadility</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>title: where esg intelligence meets shariah-compliant digital finance speakers: fahad siddiqui - ceo &amp; founder, al mabrook finance sajjeed aslam - partner, sustainadility llc usa hina nasir - partner, sustainadility llc usa in this snippet, fahad breaks down a critical distinction within the digital asset space-contrasting highly volatile cryptocurrencies with real world asset (rwa) tokens that are backed by tangible, physical assets. he explains how traditional cryptocurrencies often derive their value from market sentiment and speculation, leading to sharp price fluctuations, whereas rwa tokens are anchored in real assets such as real estate, commodities, or infrastructure. this fundamental difference not only impacts stability and risk profiles but also shapes how investors perceive value, trust, and long-term potential within these two categories of digital assets. full session :  climena middle east sajjeed aslam faraz khan mbe hina nasir kashif (kash) aqeel ahsan abdullah khan fahad siddiqui emirates nbd first abu dhabi bank (fab) abu dhabi commercial bank dubai islamic bank pakistan mashreq corporate &amp; investment banking group rakbank commercial bank of dubai abu dhabi islamic bank - egypt sharjah islamic bank ajman bank national bank of fujairah (nbf) bank of sharjah commercial bank hsbc standard chartered national bank of bahrain the saudi national bank - snb</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>37</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Fahad Siddiqui contrasts volatile cryptocurrencies with stable real world asset (RWA) tokens. • RWA tokens are backed by tangible assets like real estate and commodities. • The distinction affects stability, risk profiles, and investor perceptions of value.</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>AliveNow - Creative Tech Studio</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>46125.73963571759</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Stop Interacting. Start Co-Creating: Why TikTok Branded Effects are the Ultimate ROI Driver for 2026. 🚀
-The marketing funnel has changed. It’s no longer about getting a user to watch your ad; it’s about getting them to participate in it. If your brand is on TikTok, Branded Effects are the bridge between passive scrolling and active brand advocacy. At AliveNow, we’ve seen first-hand how immersive AR experiences transform digital campaigns into cultural moments.
-Why are Branded Effects a game-changer for Brand Managers?
-✅ Unrivaled UGC Engine: Unlike traditional ads, AR effects invite users to create content for you. This results in authentic, high-volume User Generated Content that builds trust and virality.
-✅ Low Friction, High Engagement: No third-party apps. These effects live natively in the TikTok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3D portals.
-✅ Gamification &amp; Rewards: From decibel-based challenges to AR sports games, we build experiences that drive real-world actions—like unlocking coupons or entering giveaways.
-✅ Measurable Impact: It’s not just "vibes." We track total impressions, effect uses, shares, and engagement data to ensure your campaign delivers a tangible ROI.
-Our Track Record with Branded TikTok AR effects: 
-We’ve been busy helping global leaders redefine their TikTok presence. Some of our recent work includes:
-Nestlé: A vocal-chord-powered challenge to unlock virtual rewards.
-McDonald’s: A delicious AR game catching McCrispy burgers.
-Emirates NBD: Celebrating partnerships with immersive gesture-based games.
-Colgate, Aldi, and Hellman’s: From 3D face morphing to interactive food pairings.
-The Best Part?
-Whether it’s a simple 3-day build or a complex 3D world-tracking experience, our team at AliveNow handles the entire lifecycle—from concept and design to TikTok platform approval.
-Ready to turn your audience into your biggest content creators? Let’s build something viral.
-👉 Explore our TikTok AR Gallery: https://lnkd.in/gWgcjuEd
-#TikTokMarketing #AugmentedReality #BrandedEffects #TikTokAR #TikTokBrandedEffects #DigitalMarketing #BrandStrategy #UGC #AliveNow #CreativeTech #MarketingInnovation #ARforBusiness</t>
-        </is>
-      </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
@@ -5001,27 +5005,23 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6,262</t>
-        </is>
-      </c>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/alivenow_tiktok-ar-branded-effects-for-marketing-campaigns-activity-7449452602305536000-UqHv?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFsi1KEB0NjkEVQ4jL0A7FVh21zBRaPUg9s</t>
+          <t>https://www.linkedin.com/posts/farhan-shaikh-56b9b5117_networking-dubaibusiness-emiratesnbd-activity-7449359915468529664-X36W?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACiquzIBVPCJOcn9Bc2jgkPFZKTiIkIij9Y</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>urn:li:activity:7449452602305536000</t>
+          <t>urn:li:activity:7449359915468529664</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>stop interacting. start co-creating: why tiktok branded effects are the ultimate roi driver for 2026. the marketing funnel has changed. it’s no longer about getting a user to watch your ad; it’s about getting them to participate in it. if your brand is on tiktok, branded effects are the bridge between passive scrolling and active brand advocacy. at alivenow, we’ve seen first-hand how immersive ar experiences transform digital campaigns into cultural moments. why are branded effects a game-changer for brand managers? unrivaled ugc engine: unlike traditional ads, ar effects invite users to create content for you. this results in authentic, high-volume user generated content that builds trust and virality. low friction, high engagement: no third-party apps. these effects live natively in the tiktok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3d portals. gamification &amp; rewards: from decibel-based challenges to ar sports games, we build experiences that drive real-world actions—like unlocking coupons or entering giveaways. measurable impact: it’s not just "vibes." we track total impressions, effect uses, shares, and engagement data to ensure your campaign delivers a tangible roi. our track record with branded tiktok ar effects: we’ve been busy helping global leaders redefine their tiktok presence. some of our recent work includes: nestlé: a vocal-chord-powered challenge to unlock virtual rewards. mcdonald’s: a delicious ar game catching mccrispy burgers. emirates nbd: celebrating partnerships with immersive gesture-based games. colgate, aldi, and hellman’s: from 3d face morphing to interactive food pairings. the best part? whether it’s a simple 3-day build or a complex 3d world-tracking experience, our team at alivenow handles the entire lifecycle—from concept and design to tiktok platform approval. ready to turn your audience into your biggest content creators? let’s build something viral. explore our tiktok ar gallery:  #tiktokmarketing #augmentedreality #brandedeffects #tiktokar #tiktokbrandedeffects #digitalmarketing #brandstrategy #ugc #alivenow #creativetech #marketinginnovation #arforbusiness</t>
+          <t>every journey starts with a direction. working in business banking at emirates nbd has given me the opportunity to connect with professionals, entrepreneurs, and businesses across the uae. in a fast-moving environment like dubai, building the right connections and understanding client needs makes all the difference. always open to connecting with business owners, consultants, and professionals who may require support with banking solutions. let’s connect and grow together. #networking #dubaibusiness #emiratesnbd #businessbanking #growth #uae</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>AliveNow - Creative Tech Studio</t>
+          <t>Farhan Shaikh</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>stop interacting. start co-creating: why tiktok branded effects are the ultimate roi driver for 2026. the marketing funnel has changed. it’s no longer about getting a user to watch your ad; it’s about getting them to participate in it. if your brand is on tiktok, branded effects are the bridge between passive scrolling and active brand advocacy. at alivenow, we’ve seen first-hand how immersive ar experiences transform digital campaigns into cultural moments. why are branded effects a game-changer for brand managers? unrivaled ugc engine: unlike traditional ads, ar effects invite users to create content for you. this results in authentic, high-volume user generated content that builds trust and virality. low friction, high engagement: no third-party apps. these effects live natively in the tiktok camera, allowing users to engage with your brand in seconds using hand gestures, face tracking, or 3d portals. gamification &amp; rewards: from decibel-based challenges to ar sports games, we build experiences that drive real-world actions—like unlocking coupons or entering giveaways. measurable impact: it’s not just "vibes." we track total impressions, effect uses, shares, and engagement data to ensure your campaign delivers a tangible roi. our track record with branded tiktok ar effects: we’ve been busy helping global leaders redefine their tiktok presence. some of our recent work includes: nestlé: a vocal-chord-powered challenge to unlock virtual rewards. mcdonald’s: a delicious ar game catching mccrispy burgers. emirates nbd: celebrating partnerships with immersive gesture-based games. colgate, aldi, and hellman’s: from 3d face morphing to interactive food pairings. the best part? whether it’s a simple 3-day build or a complex 3d world-tracking experience, our team at alivenow handles the entire lifecycle—from concept and design to tiktok platform approval. ready to turn your audience into your biggest content creators? let’s build something viral. explore our tiktok ar gallery:  #tiktokmarketing #augmentedreality #brandedeffects #tiktokar #tiktokbrandedeffects #digitalmarketing #brandstrategy #ugc #alivenow #creativetech #marketinginnovation #arforbusiness</t>
+          <t>every journey starts with a direction. working in business banking at emirates nbd has given me the opportunity to connect with professionals, entrepreneurs, and businesses across the uae. in a fast-moving environment like dubai, building the right connections and understanding client needs makes all the difference. always open to connecting with business owners, consultants, and professionals who may require support with banking solutions. let’s connect and grow together. #networking #dubaibusiness #emiratesnbd #businessbanking #growth #uae</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Branded effects on TikTok drive user-generated content and brand engagement. • AR experiences enable low-friction interaction without third-party apps. • Campaigns provide measurable ROI through tracked impressions and engagement data.</t>
+          <t>working in business banking at emirates nbd has given me the opportunity to connect with professionals, entrepreneurs, and businesses across the uae. • always open to connecting with business owners, consultants, and professionals who may require support with banking solutions. • in a fast-moving environment like dubai, building the right connections and understanding client needs makes all the difference.</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5119,7 +5119,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/priya-mahesh-841807165_corporatestrategies-activity-7449517378004164609-l0DM?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFEu2ZMBVTfn86Zv1-EI4L3EI29mXcRrhtA</t>
+          <t>https://www.linkedin.com/posts/priya-mahesh-841807165_corporatestrategies-activity-7449517378004164609-l0DM?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADpvVoYBUx2AZFR---ZdAR9LHeZnQHPr4i4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Cooking strategies discussed from "citi" to "enbd" in UAE. • Expressing gratitude for the journey.</t>
+          <t>cooking strategies from "citi" till "enbd", in uae. • grateful for the journey.</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/thehanginghouse_after-his-highness-sheikh-mohammed-bin-rashid-activity-7449509855272468480-250Z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFEu2ZMBVTfn86Zv1-EI4L3EI29mXcRrhtA</t>
+          <t>https://www.linkedin.com/posts/thehanginghouse_after-his-highness-sheikh-mohammed-bin-rashid-activity-7449509855272468480-250Z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADpvVoYBUx2AZFR---ZdAR9LHeZnQHPr4i4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Sheikh Mohammed bin Rashid Al Maktoum urged flag raising on April 9. • National pride was reflected across UAE's skyline and online platforms. • Brands like Talabat and ENBD participated in the collective expression of pride.</t>
+          <t>you could see it across the skyline, across workplaces, and across the country’s visual language online too, with brands and platforms reflecting the moment in real time. • in people and brands choosing to reflect the same feeling at the same time. • from talabat to enbd x to adnoc, the digital layer mirrored what was already happening on the ground.</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -5346,7 +5346,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/birceyakut_iaovaexkontrol-takaftmruhu-denizbank-activity-7449424568110342146-PnjY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFEu2ZMBVTfn86Zv1-EI4L3EI29mXcRrhtA</t>
+          <t>https://www.linkedin.com/posts/birceyakut_iaovaexkontrol-takaftmruhu-denizbank-activity-7449424568110342146-PnjY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADpvVoYBUx2AZFR---ZdAR9LHeZnQHPr4i4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Strong team spirit and shared vision emphasized at the townhall. • Appreciation expressed to all contributors for their efforts. • Focus on building better together.</t>
+          <t>"hi̇ç kontrolsüz olur mu?" townhall’da güçlü ekip ruhunu ve ortak vizyonu bir kez daha hissettik. • #i̇çkontrol #takımruhu #denizbank #i̇lerisisensin #i̇lerisideniz #enbd • birlikte daha iyisini inşa etmek için buradayız.</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>383,236</t>
+          <t>383,237</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_%D8%A7%D9%84%D9%88%D8%B9%D9%8A-%D8%A7%D9%84%D9%85%D8%A7%D9%84%D9%8A-activity-7449697955168624640-p0g_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADe8BX4BelwWTQ01uSbSHmL-HZjOP4FB6iw</t>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_%D8%A7%D9%84%D9%88%D8%B9%D9%8A-%D8%A7%D9%84%D9%85%D8%A7%D9%84%D9%8A-activity-7449697955168624640-p0g_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFA4xNYBPolZtMq8tAr6-_9nQ3iDzF2QJTE</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Money grows better with time, balance, and proper diversification. • Diversifying investments and long-term thinking enhance stability. • Small steps today can lead to stronger future results.</t>
+          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب. • تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر. • خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>383,236</t>
+          <t>383,237</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_eifinancialwellbeing-smartmoneymindset-emiratesislamic-activity-7449697954820620288-sOXS?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADe8BX4BelwWTQ01uSbSHmL-HZjOP4FB6iw</t>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_eifinancialwellbeing-smartmoneymindset-emiratesislamic-activity-7449697954820620288-sOXS?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFA4xNYBPolZtMq8tAr6-_9nQ3iDzF2QJTE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Focus on financial well-being and smart money management. • Emphasis on Emirates Islamic's services and offerings. • Encouragement for a proactive approach to personal finance.</t>
+          <t>#eifinancialwellbeing #smartmoneymindset #emiratesislamic</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>383,236</t>
+          <t>383,237</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_spreading-investments-and-thinking-long-termmp4-activity-7449697954820550656-JCm9?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADe8BX4BelwWTQ01uSbSHmL-HZjOP4FB6iw</t>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_spreading-investments-and-thinking-long-termmp4-activity-7449697954820550656-JCm9?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFA4xNYBPolZtMq8tAr6-_9nQ3iDzF2QJTE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Time, balance, and diversification enhance investment growth. • Long-term thinking supports steadier financial progress. • Small steps today lead to stronger future outcomes.</t>
+          <t>spreading investments and thinking long term can help create steadier progress along the way. • money grows best when given time, balance, and the right mix. • small steps today can support stronger outcomes tomorrow.</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>383,236</t>
+          <t>383,237</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aeuaegaezaesaerabraepaesaetaepaesaeyaer-aepaesaesaetaeqaeyaepabraepaesaetaepaesaey-activity-7449697954602360832-sC_d?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADe8BX4BelwWTQ01uSbSHmL-HZjOP4FB6iw</t>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aeuaegaezaesaerabraepaesaetaepaesaeyaer-aepaesaesaetaeqaeyaepabraepaesaetaepaesaey-activity-7449697954602360832-sC_d?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFA4xNYBPolZtMq8tAr6-_9nQ3iDzF2QJTE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Focus on financial literacy in the UAE. • Emphasis on Islamic finance principles. • Engaging community discussions on financial perspectives.</t>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>383,236</t>
+          <t>383,237</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aeuaegaezaesaerabraepaesaetaepaesaeyaer-aepaesaesaetaeqaeyaepabraepaesaetaepaesaey-activity-7449682858396536833-ThM9?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADe8BX4BelwWTQ01uSbSHmL-HZjOP4FB6iw</t>
+          <t>https://www.linkedin.com/posts/emirates-islamic-bank_aeuaegaezaesaerabraepaesaetaepaesaeyaer-aepaesaesaetaeqaeyaepabraepaesaetaepaesaey-activity-7449682858396536833-ThM9?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFA4xNYBPolZtMq8tAr6-_9nQ3iDzF2QJTE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Weekly perspective for mindful financial living. • Focus on financial education and well-being. • Emphasis on achieving financial balance.</t>
+          <t>a step toward a more mindful financial week. • #eifinancialwellbeing #smartmoneymindset #emiratesislamic • #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي your weekly perspective.</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6021,7 +6021,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mohamed-ashraf-041044399_personal-finance-credit-cards-in-uae-activity-7449697004374401024-hwty?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEfPoy8Blxw4H0aFW4fd5iMfr22NPEYw0HU</t>
+          <t>https://www.linkedin.com/posts/mohamed-ashraf-041044399_personal-finance-credit-cards-in-uae-activity-7449697004374401024-hwty?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADQAlkkBUUvaZtSkulxD0ZwdxpTp1pGWLjk</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Easy process and fast approval for personal finance and credit cards in UAE. • Best offers available through Emirates Islamic. • Direct message for more details.</t>
+          <t>personal finance &amp; credit cards in uae easy process fast approval best offers working with emirates islamic dm me for more details</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6146,7 +6146,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/feed/update/urn:li:activity:7449691237575471104?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEfPoy8Blxw4H0aFW4fd5iMfr22NPEYw0HU</t>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7449691237575471104?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADQAlkkBUUvaZtSkulxD0ZwdxpTp1pGWLjk</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Pakistan plans to launch its first panda bond next month for $250 million. • A $3.5 billion facility in the UAE needs replacement. • Debt options include Islamic sukuk and eurobonds.</t>
+          <t>$3.5 billion facility has to be replaced. • the association of southeast asian nations (asean). • the first of a planned $1 billion programme.</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/personadock_shayan-kazmi-is-a-product-manager-at-emirates-activity-7449449019732283392-LjHW?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEfPoy8Blxw4H0aFW4fd5iMfr22NPEYw0HU</t>
+          <t>https://www.linkedin.com/posts/personadock_shayan-kazmi-is-a-product-manager-at-emirates-activity-7449449019732283392-LjHW?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADQAlkkBUUvaZtSkulxD0ZwdxpTp1pGWLjk</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Shayan Kazmi manages financial products at Emirates Islamic in the assets segment. • His experience includes product lifecycle management and customer experience optimization. • Emphasis needed on measurable impact to differentiate in a competitive market.</t>
+          <t>to stand out, the focus needs to shift toward measurable impact—portfolio growth figures, conversion improvements in digital channels, or efficiency gains in processes. • without that, the profile risks sounding generic in a highly competitive space where most professionals claim similar competencies but few demonstrate clear, quantifiable outcomes. • however, the positioning leans heavily on broad functional claims that are common across banking product roles.</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>632,104</t>
+          <t>632,106</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/adcbofficial_%D8%AA%D8%B9%D8%B1%D9%81-%D8%B9%D9%84%D9%89-%D8%AE%D8%B7%D9%88%D8%A7%D8%AA-%D8%AA%D8%AD%D8%AF%D9%8A%D8%AB-%D8%B1%D9%82%D9%85-%D9%87%D8%A7%D8%AA%D9%81%D9%83-%D8%A7%D9%84%D9%85%D8%AA%D8%AD%D8%B1%D9%83-%D9%85%D9%86-activity-7449500529103331328-C4AD?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWuLVEBI99rxrHle4hYELPY12Zi8VCwl_0</t>
+          <t>https://www.linkedin.com/posts/adcbofficial_%D8%AA%D8%B9%D8%B1%D9%81-%D8%B9%D9%84%D9%89-%D8%AE%D8%B7%D9%88%D8%A7%D8%AA-%D8%AA%D8%AD%D8%AF%D9%8A%D8%AB-%D8%B1%D9%82%D9%85-%D9%87%D8%A7%D8%AA%D9%81%D9%83-%D8%A7%D9%84%D9%85%D8%AA%D8%AD%D8%B1%D9%83-%D9%85%D9%86-activity-7449500529103331328-C4AD?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEIIGLABexO8QDOm_sU3-Yzd18P3nBuFBJ4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Update your mobile number via Abu Dhabi Commercial Bank's smartphone app. • Follow specific steps provided in the app for the update process. • Ensure your information is current for banking communications.</t>
+          <t>تعرف على خطوات تحديث رقم هاتفك المتحرك من خلال تطبيق بنك أبوظبي التجاري للهواتف الذكية.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>632,104</t>
+          <t>632,106</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/adcbofficial_how-to-update-your-number-on-adcb-mobile-activity-7449464008660885504-_V6y?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADWuLVEBI99rxrHle4hYELPY12Zi8VCwl_0</t>
+          <t>https://www.linkedin.com/posts/adcbofficial_how-to-update-your-number-on-adcb-mobile-activity-7449464008660885504-_V6y?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEIIGLABexO8QDOm_sU3-Yzd18P3nBuFBJ4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Open the ADCB mobile banking app. • Navigate to the profile settings section. • Select the option to update your phone number.</t>
+          <t>how to update your number on adcb mobile banking app?</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -6590,12 +6590,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>295,798</t>
+          <t>295,799</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/commercial-bank-of-dubai_customerexperience-digitalbanking-cbduae-activity-7449701508226486273-fPKe?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGNYwmMBHH05CVFu0KpJR4gGCaJ72HAoAEU</t>
+          <t>https://www.linkedin.com/posts/commercial-bank-of-dubai_customerexperience-digitalbanking-cbduae-activity-7449701508226486273-fPKe?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFoEmG0BlJVpLe7bG1EmFJMzeLLMmRltfRo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Focus on simplifying and speeding up banking experiences for customers. • Key initiatives include digital onboarding, real-time payments, and open finance. • Aisha Almazrouei discussed these strategies in an interview with Al Bayan.</t>
+          <t>we are building a bank that’s simpler, faster, and more intelligent, removing friction from the moments that matter most and designing experiences that work best for our customers. • يمكنكم الاطلاع على المقابلة الكاملة على صحيفة البيان: #تجربة_المتعامل #الخدمات_المصرفية_الرقمية #ندعم_نموكم</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>295,798</t>
+          <t>295,799</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/commercial-bank-of-dubai_salik-fine-scams-activity-7449467982378065920-LtXE?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGNYwmMBHH05CVFu0KpJR4gGCaJ72HAoAEU</t>
+          <t>https://www.linkedin.com/posts/commercial-bank-of-dubai_salik-fine-scams-activity-7449467982378065920-LtXE?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFoEmG0BlJVpLe7bG1EmFJMzeLLMmRltfRo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Scams now appear official, urgent, and convincing. • Follow the S.A.F.E. principle: Secure, Activate alerts, Follow trusted sources, Educate. • Report fraud to CBD's contact center: 600 575 556.</t>
+          <t>report fraud – contact cbd’s contact centre: 600 575 556 #cbduae #fraudalert #safewithcbd عمليات الاحتيال لم تعد واضحة كما كانت. • protect yourself: • pay only through official channels • avoid clicking on unknown links • do not download unfamiliar apps • confirm with the relevant authority pause. • scams don’t look like scams anymore.</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/adcbegypt_happy-easter-wishing-you-bright-days-and-activity-7449397317226647552-uFSz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFYWoeIBsLIYtp6X3MC4fMTJk3rTU5SiVdk</t>
+          <t>https://www.linkedin.com/posts/adcbegypt_happy-easter-wishing-you-bright-days-and-activity-7449397317226647552-uFSz?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAF7quwEBfPRF8nB_kpxkNct9tNzYDGlAtMU</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Wishing a happy Easter and bright days. • "شم نسيم سعيد" translates to "Happy Spring Breeze." • "كل عام وأنتم بخير" means "Wishing you well every year."</t>
+          <t>wishing you bright days and fresh beginnings!</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/sosaron-treasury-mastery_cyberrisk-treasurytransformation-geopoliticalrisk-activity-7449713089152733184-iKbP?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEQ8vnUBjKB3AkorBAdU-FLQ_OdUTF5zO8E</t>
+          <t>https://www.linkedin.com/posts/sosaron-treasury-mastery_cyberrisk-treasurytransformation-geopoliticalrisk-activity-7449713089152733184-iKbP?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB8kdkMBF6Kz93qH-RaPDvgd6OxdCy82p3U</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Since February 28, 2026, Iran-linked actors launched 1,583 cyber incidents targeting banks. • 144 attacks specifically targeted the financial sector, including major Gulf institutions. • Historical precedent shows significant operational losses from past Iranian cyber campaigns.</t>
+          <t>the direct hit to treasury real-time dashboards, api bank connectivity, and automated payment/reconciliation engines are becoming single points of failure. • segment critical treasury infrastructure — isolate real-time payment and liquidity systems from public-facing networks (zero-trust architecture is no longer optional). • integrate real-time threat intelligence feeds directly into treasury operations — not just compliance — so teams can pre-emptively throttle high-risk corridors.</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7095,7 +7095,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mohammed-essam-20469033b_%D8%A7%D9%84%D8%B3%D9%84%D8%A7%D9%85-%D8%B9%D9%84%D9%8A%D9%83%D9%85-%D9%88%D8%B1%D8%AD%D9%85%D9%87-%D8%A7%D9%84%D9%84%D9%87-%D9%88%D8%A8%D8%B1%D9%83%D8%A7%D8%AA%D9%87-%D8%AF%D8%A9-cv-%D8%A8%D8%AA%D8%A7%D8%B9%D9%89-activity-7449547852105641984-9hIk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEQ8vnUBjKB3AkorBAdU-FLQ_OdUTF5zO8E</t>
+          <t>https://www.linkedin.com/posts/mohammed-essam-20469033b_%D8%A7%D9%84%D8%B3%D9%84%D8%A7%D9%85-%D8%B9%D9%84%D9%8A%D9%83%D9%85-%D9%88%D8%B1%D8%AD%D9%85%D9%87-%D8%A7%D9%84%D9%84%D9%87-%D9%88%D8%A8%D8%B1%D9%83%D8%A7%D8%AA%D9%87-%D8%AF%D8%A9-cv-%D8%A8%D8%AA%D8%A7%D8%B9%D9%89-activity-7449547852105641984-9hIk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB8kdkMBF6Kz93qH-RaPDvgd6OxdCy82p3U</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Seeking job or internship opportunities in banking and financial institutions. • Interested in positions at Banque Misr, NBE, and QNB Egypt. • Relevant experience includes senior manager role in MEP.</t>
+          <t>abu ruka mba,pmp,cldr,rmp as senior manager mep‏ eq bank banque misr</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7218,7 +7218,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/taha-shaikh-87a008259_fraudalert-cybercrime-bankingsecurity-activity-7449451383419813889-K9tq?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEQ8vnUBjKB3AkorBAdU-FLQ_OdUTF5zO8E</t>
+          <t>https://www.linkedin.com/posts/taha-shaikh-87a008259_fraudalert-cybercrime-bankingsecurity-activity-7449451383419813889-K9tq?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAB8kdkMBF6Kz93qH-RaPDvgd6OxdCy82p3U</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>AED 5,187 was put on hold due to unauthorized transactions on April 11. • Funds were transferred to an e&amp; money account and then to Kenya. • The user did not authorize transactions, raising concerns about banking security.</t>
+          <t>i was shocked to learn that the money was transferred to an e&amp; money account and then further transferred to kenya. • this is about trust, safety, and the hard-earned money of millions of people living and working in the uae. • this raises serious and frightening questions: how can money be transferred without my knowledge or consent?</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7313,7 +7313,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F59" t="n">
         <v>33</v>
@@ -7329,7 +7329,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/hassan-elwassef-39b138222_growth-promotion-customerexperience-activity-7449546482657075200-VW1s?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAENhLHsBEHxfz3On9AM1o7H2RBs4fVhKXic</t>
+          <t>https://www.linkedin.com/posts/hassan-elwassef-39b138222_growth-promotion-customerexperience-activity-7449546482657075200-VW1s?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAELLl2gBDtzazHYxDxU0-7oyZVvBcKlJfhk</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Promoted from Officer B to Officer A at ADCB. • Role evolved to Customer Care &amp; Service Recovery. • Acknowledged support from Mrs. Inès Kadri and Ramy El-Shahawy.</t>
+          <t>excited to share that i’ve been promoted from officer b to officer a at adcb additionally, my role has evolved from customer care officer to customer care &amp; service recovery. • this step reflects continuous learning, overcoming challenges, and delivering value throughout my journey. • inès kadri, and ramy el-shahawy, for their trust, continuous support, and guidance it truly made a difference.</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7438,7 +7438,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/muna-alameri-b7a92b132_im-truly-grateful-for-my-journey-at-adib-activity-7449438756417228800-AM2Z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAENhLHsBEHxfz3On9AM1o7H2RBs4fVhKXic</t>
+          <t>https://www.linkedin.com/posts/muna-alameri-b7a92b132_im-truly-grateful-for-my-journey-at-adib-activity-7449438756417228800-AM2Z?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAELLl2gBDtzazHYxDxU0-7oyZVvBcKlJfhk</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="R60" t="n">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Spent meaningful years at ADIB learning and growing. • Starting a new role as an analyst in sanctions operations at ADCB. • Grateful for past experiences and looking forward to future opportunities.</t>
+          <t>i’m truly grateful for my journey at adib, where i spent meaningful years learning, growing, and building experiences that shaped who i am today. • it was more than just a workplace, it was a chapter filled with lessons, challenges, and people i will always appreciate. • today, i’m excited to begin a new journey as an analyst – sanctions operations at adcb.</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7556,7 +7556,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/vipin-k-krishnan-827398254_abu-dhabi-commercial-bank-adcb-to-set-up-activity-7449393745009192960-XmME?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAENhLHsBEHxfz3On9AM1o7H2RBs4fVhKXic</t>
+          <t>https://www.linkedin.com/posts/vipin-k-krishnan-827398254_abu-dhabi-commercial-bank-adcb-to-set-up-activity-7449393745009192960-XmME?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAELLl2gBDtzazHYxDxU0-7oyZVvBcKlJfhk</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>ADCB plans to launch a subsidiary bank in Kazakhstan for global expansion. • Expansion enhances competition and introduces new financial products in local markets. • Growing demand for talent in digital banking and fintech across emerging markets.</t>
+          <t>fintech growth is increasingly being shaped by cross-border expansion and regional market diversification.​ adcb’s plan …</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7664,7 +7664,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/amani-mohammed-3093a1242_adcb-activity-7449372903126573056-I_Cq?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAENhLHsBEHxfz3On9AM1o7H2RBs4fVhKXic</t>
+          <t>https://www.linkedin.com/posts/amani-mohammed-3093a1242_adcb-activity-7449372903126573056-I_Cq?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAELLl2gBDtzazHYxDxU0-7oyZVvBcKlJfhk</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Grateful for being part of a supportive team. • Received a birthday surprise that made my day. • Celebrating small moments is valued.</t>
+          <t>grateful for being part of a team that celebrates the little moments thank you for the birthday surprise, it truly made my day #adcb</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -7795,7 +7795,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mohamed-rezk2702_cv-activity-7449365767927631874-5Fz7?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADvgSHABngS0mEvug5lhcnaG-7KE0gCvQCo</t>
+          <t>https://www.linkedin.com/posts/mohamed-rezk2702_cv-activity-7449365767927631874-5Fz7?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAADDbKyUBliJAU6h5u1uTmkzg1K3FEkbghHU</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Recent graduate in Accounting from Benha University with a "Very Good" grade. • Gained practical experience through internships at Banque Misr and Banque du Caire. • Seeking a junior accountant position and open to advice or opportunities.</t>
+          <t>حاليًا بدور على فرصة شغل كمحاسب مبتدئ (junior accountant)، وأي دعم أو نصيحة أو فرصة هتكون محل تقدير كبير.</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -7903,7 +7903,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/sirajp_banking-just-got-easier-it-starts-with-a-activity-7449675361640050688-dg3j?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
+          <t>https://www.linkedin.com/posts/sirajp_banking-just-got-easier-it-starts-with-a-activity-7449675361640050688-dg3j?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD1A7nsBKG4VkC8Ktkm8Kub912oB0ljxK4I</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>ADIB offers digital banking services. • Contact them for assistance. • Hashtag used: #adib.</t>
+          <t>#adib #digitalbanking​​​​​​​​​​​​​​​​ adib - abu dhabi islamic bank</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/theiilm_sukuk-commercialpapers-abcp-activity-7449658667085299712-9PkK?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
+          <t>https://www.linkedin.com/posts/theiilm_sukuk-commercialpapers-abcp-activity-7449658667085299712-9PkK?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD1A7nsBKG4VkC8Ktkm8Kub912oB0ljxK4I</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>IILM to auction short-term ṣukūk across multiple tenors. • Auction date: Monday, 3:00 PM to 6:00 PM (Kuala Lumpur time). • Contact primary dealers for purchasing inquiries.</t>
+          <t>in short-term ṣukūk across tenors: 2-week 2-month 3-month 6-month 9-month auction date: monday, ⏰ time: 3:00 pm to 6:00 pm (kuala lumpur time) for enquiries, kindly reach out to issuance@iilm.com. • #sukuk #commercialpapers #abcp #islamicfinance #moneymarket #liquiditymanagement #iilm #investors #primarydealers #centralbanks #islamicbanking #issuance #auction • the iilm - international islamic liquidity management will auction up to .</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F66" t="n">
         <v>12</v>
       </c>
       <c r="G66" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/rasha-wael-55a13a403_%D8%A7%D9%86%D8%A7-%D8%B2%D9%88%D8%AC%D9%8A-%D9%85%D8%AD%D8%A7%D8%B3%D8%A8-%D8%B9%D8%A7%D9%85-%D8%A8%D9%8A%D8%AF%D9%88%D8%B1-%D8%B9-%D8%B4%D8%BA%D9%84-%D8%A8%D9%82%D8%A7%D9%84%D9%87-%D9%81%D8%AA%D8%B1%D8%A9-activity-7449424016093708289-zT9X?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
+          <t>https://www.linkedin.com/posts/rasha-wael-55a13a403_%D8%A7%D9%86%D8%A7-%D8%B2%D9%88%D8%AC%D9%8A-%D9%85%D8%AD%D8%A7%D8%B3%D8%A8-%D8%B9%D8%A7%D9%85-%D8%A8%D9%8A%D8%AF%D9%88%D8%B1-%D8%B9-%D8%B4%D8%BA%D9%84-%D8%A8%D9%82%D8%A7%D9%84%D9%87-%D9%81%D8%AA%D8%B1%D8%A9-activity-7449424016093708289-zT9X?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD1A7nsBKG4VkC8Ktkm8Kub912oB0ljxK4I</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Husband secured a job after a long search and multiple interviews. • Credit given to Dr. Ahmed Abdelkader for enhancing his CV and LinkedIn profile. • Highlighting the importance of professional assistance in job applications.</t>
+          <t>انا زوجي محاسب عام بيدور ع شغل بقاله فترة كبيرة جدا بعد ما ساب شغله الأخير لكن مفيش اي رد واتحطينا ف ظروف صعبة وانهاردا …</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/bigprojectme_adib-abu-dhabi-islamic-bank-strengthens-activity-7449400512136794113-9NYM?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
+          <t>https://www.linkedin.com/posts/bigprojectme_adib-abu-dhabi-islamic-bank-strengthens-activity-7449400512136794113-9NYM?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD1A7nsBKG4VkC8Ktkm8Kub912oB0ljxK4I</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>ADIB and Jubail Island Investment Company signed an MOU for financial services enhancement. • The agreement focuses on financing properties within Jubail Island. • Key representatives include Mohamed Abdel Bary and Mounir Haidar.</t>
+          <t>mohamed abdel bary, cfa | mounir haidar , p.e.</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8373,7 +8373,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mohamed-said-ba818924b_backend-dotnet-cleancode-activity-7449399542883553280-DRrY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAC0JzDIBL1NztyGLeDkT5vdSluBYkXmJ-jI</t>
+          <t>https://www.linkedin.com/posts/mohamed-said-ba818924b_backend-dotnet-cleancode-activity-7449399542883553280-DRrY?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAD1A7nsBKG4VkC8Ktkm8Kub912oB0ljxK4I</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Using URL for IDs improves logging and caching efficiency. • Body is for large, sensitive data; enhances security and organization. • Query parameters enable filtering and sorting without altering data structure.</t>
+          <t>mohamed ahmed saad mostafa anis maged abousekin mostafa anis adib - abu dhabi islamic bank @ #backend #dotnet #cleancode #api #webdevelopment #softwareengineering #aspnetcore • performance: الـ api gateways بتفهم طلبك من الـ url أسرع بكتير من إنها تفتح الـ body وتفتش فيه. • لما ببعت الـ id في الـ url (زي /api/orders/5)، أنا بقول للسيرفر وللـ gateway بوضوح إني بتعامل مع مورد محدد.</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F69" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -8482,7 +8482,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/ca-balakrishnan-sl-8ba93a1b_gratitude-leadership-businessbanking-activity-7449505666668609536-3-hm?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFFHfikBhIO9fYltl6JsMMGlm8UMt2G85sM</t>
+          <t>https://www.linkedin.com/posts/ca-balakrishnan-sl-8ba93a1b_gratitude-leadership-businessbanking-activity-7449505666668609536-3-hm?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Joined Commercial Bank of Dubai as Head of Business Banking Credit. • Previously spent 17.5 years at Abu Dhabi Commercial Bank. • Held roles as Head of SME Products and Head of SME Credit at ADCB.</t>
+          <t>after a fulfilling 17.5-year journey with abu dhabi commercial bank (adcb), i’m pleased to share that i have taken on a new role as head of business banking credit at commercial bank of dubai (cbd). • during my time at adcb, i had the privilege of serving as head of sme products and head of sme credit—experiences that have been instrumental in shaping my professional journey. • i look forward to this new chapter and to contributing meaningfully at cbd.</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -8590,7 +8590,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/andrii-zhovtiak-24b7a8342_cbduae-aeqaeuaerabraexaeqaeyabraepaesaesaeuaepaezaey-activity-7449430159750750208-vDby?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFFHfikBhIO9fYltl6JsMMGlm8UMt2G85sM</t>
+          <t>https://www.linkedin.com/posts/andrii-zhovtiak-24b7a8342_cbduae-aeqaeuaerabraexaeqaeyabraepaesaesaeuaepaezaey-activity-7449430159750750208-vDby?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>UAE institutions raised the flag in response to Sheikh Mohammed bin Rashid Al Maktoum's call. • CBD exemplifies banks as part of the broader social fabric in the UAE. • The event reflects a shared sense of identity and unity across nationalities.</t>
+          <t>what stands out to me is how banks like cbd aren’t just financial institutions here, but part of the broader social fabric that actively participates in moments like these. • a simple but powerful reminder from commercial bank of dubai of what makes the uae unique.</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3,722</t>
+          <t>3,724</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/uaegloballeaders_uaegloballeaders-globalleadersinc-banking-activity-7449392189261987840-_ioV?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFFHfikBhIO9fYltl6JsMMGlm8UMt2G85sM</t>
+          <t>https://www.linkedin.com/posts/uaegloballeaders_uaegloballeaders-globalleadersinc-banking-activity-7449392189261987840-_ioV?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEk8-z0B7dM2q5buqGHbCZriZXOx2kEtc08</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Ghada Ahmed is a virtual relationship manager at Abu Dhabi Commercial Bank (ADCB). • She previously worked as a relationship officer at RAKBANK in the UAE. • Ghada holds a Bachelor of Business Administration in International Business.</t>
+          <t>we are proud to recognize ghada ahmed, a dedicated banking professional with strong expertise in relationship management, sme banking, and credit analysis. • ghada ahmed holds a bachelor of business administration in international business from sadat academy for management sciences, further strengthening her foundation in finance and banking. • we celebrate ghada ahmed commitment to excellence, client-centric approach, and her growing impact in the banking industry across the uae.</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>104,528</t>
+          <t>104,534</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/fabmisr_%D8%A8%D9%86%D9%83-%D8%A3%D8%A8%D9%88%D8%B8%D8%A8%D9%8A-%D8%A7%D9%84%D8%A3%D9%88%D9%84-%D9%85%D8%B5%D8%B1-%D8%A8%D9%8A%D8%AA%D9%85%D9%86%D9%89-%D9%84%D9%83%D9%85-%D8%B4%D9%85-%D8%A7%D9%84%D9%86%D8%B3%D9%8A%D9%85-activity-7449381038587310081-fQf_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABJnN1EBg8SkzCDxZWBl3ARKtQSsamhRgWE</t>
+          <t>https://www.linkedin.com/posts/fabmisr_%D8%A8%D9%86%D9%83-%D8%A3%D8%A8%D9%88%D8%B8%D8%A8%D9%8A-%D8%A7%D9%84%D8%A3%D9%88%D9%84-%D9%85%D8%B5%D8%B1-%D8%A8%D9%8A%D8%AA%D9%85%D9%86%D9%89-%D9%84%D9%83%D9%85-%D8%B4%D9%85-%D8%A7%D9%84%D9%86%D8%B3%D9%8A%D9%85-activity-7449381038587310081-fQf_?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFNyTjcB_yJkFzIRpZWxRoKXQFPJwk3LyhQ</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank Egypt wishes you a happy Sham El-Nessim. • Celebrating the Spring Holidays.</t>
+          <t>بنك أبوظبي الأول مصر بيتمنى لكم شم النسيم وأعياد الربيع سعيدة</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -8927,7 +8927,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/kishore-v-a08b881b_first-abu-dhabi-bank-fab-i-would-like-activity-7449363251819282432-tNYl?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAABJnN1EBg8SkzCDxZWBl3ARKtQSsamhRgWE</t>
+          <t>https://www.linkedin.com/posts/kishore-v-a08b881b_first-abu-dhabi-bank-fab-i-would-like-activity-7449363251819282432-tNYl?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAFNyTjcB_yJkFzIRpZWxRoKXQFPJwk3LyhQ</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>FAB's Gems Legacy Card was initially advertised as lifetime free. • Customer charged AED 399 annual fee without prior communication or consent. • Concerns raised about transparency and policy changes after onboarding.</t>
+          <t>however, the bank appears to have changed the policy in between, and i have now been charged an annual subscription fee of aed 399 without any clear prior communication or consent. • first abu dhabi bank (fab) i would like to share a concerning experience with first abu dhabi bank (fab) regarding the gems legacy card. • customers rely on the terms provided at the time of subscription, and any deviation without proper notice impacts trust.</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -9005,13 +9005,685 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>Carla Blondel</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46126.4631515625</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Proud moment 🤍 
+Seeing the “Together We Move Forward” campaign with First Abu Dhabi Bank (FAB) come to life out in the real world felt special. 🙏🏼
+There is something powerful about being part of a message that reflects unity and resilience. 🇦🇪 
+Even during challenging times, the UAE continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. Always moving forward. ✨</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/carla-blondel_proud-moment-seeing-the-together-we-activity-7449714795668250625-AWup?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAnqdHEBFhqGaTrppCJUDaUVNvGCvqYCUps</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449714795668250625</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>FAB</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>proud moment seeing the “together we move forward” campaign with first abu dhabi bank (fab) come to life out in the real world felt special. there is something powerful about being part of a message that reflects unity and resilience. even during challenging times, the uae continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. always moving forward.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Carla Blondel</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>proud moment seeing the “together we move forward” campaign with first abu dhabi bank (fab) come to life out in the real world felt special. there is something powerful about being part of a message that reflects unity and resilience. even during challenging times, the uae continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. always moving forward.</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>73</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>proud moment seeing the “together we move forward” campaign with first abu dhabi bank (fab) come to life out in the real world felt special. • even during challenging times, the uae continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. • there is something powerful about being part of a message that reflects unity and resilience.</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>3. First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>German Emirati Joint Council for Industry &amp; Commerce (AHK)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46126.45378488426</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>We are very pleased to give a warm welcome to a new AHK Member.
+We are pleased to welcome First Abu Dhabi Bank (FAB) as part of our growing network.
+First Abu Dhabi Bank (FAB) is the UAE’s global bank, and one of the world’s largest and safest financial institutions, with an international network that spans five continents and a presence in 20 markets to facilitate cross-border liquidity, trade, and investment flows. With the strongest combined credit rating among any other bank in the MENA region (Aa3/AA-/AA- by Moody’s, S&amp;P, and Fitch, respectively, with a stable outlook) and total assets of AED 1.34 trillion (USD 366 billion) as of June-end 2025, FAB offers an extensive range of tailor-made products and services to meet the banking needs of our customers in the UAE and the international markets.
+For more information www.bankfab.com
+Mathias Seidel &amp; Sossy Hamouche</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20,902</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/german-emirati-joint-council-for-industry-and-commerce-ahk-_we-are-very-pleased-to-give-a-warm-welcome-activity-7449711401297719296-rFcx?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAnqdHEBFhqGaTrppCJUDaUVNvGCvqYCUps</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449711401297719296</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>FAB</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>we are very pleased to give a warm welcome to a new ahk member. we are pleased to welcome first abu dhabi bank (fab) as part of our growing network. first abu dhabi bank (fab) is the uae’s global bank, and one of the world’s largest and safest financial institutions, with an international network that spans five continents and a presence in 20 markets to facilitate cross-border liquidity, trade, and investment flows. with the strongest combined credit rating among any other bank in the mena region (aa3/aa-/aa- by moody’s, s&amp;p, and fitch, respectively, with a stable outlook) and total assets of aed 1.34 trillion (usd 366 billion) as of june-end 2025, fab offers an extensive range of tailor-made products and services to meet the banking needs of our customers in the uae and the international markets. for more information  mathias seidel &amp; sossy hamouche</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>German Emirati Joint Council for Industry &amp; Commerce (AHK)</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>we are very pleased to give a warm welcome to a new ahk member. we are pleased to welcome first abu dhabi bank (fab) as part of our growing network. first abu dhabi bank (fab) is the uae’s global bank, and one of the world’s largest and safest financial institutions, with an international network that spans five continents and a presence in 20 markets to facilitate cross-border liquidity, trade, and investment flows. with the strongest combined credit rating among any other bank in the mena region (aa3/aa-/aa- by moody’s, s&amp;p, and fitch, respectively, with a stable outlook) and total assets of aed 1.34 trillion (usd 366 billion) as of june-end 2025, fab offers an extensive range of tailor-made products and services to meet the banking needs of our customers in the uae and the international markets. for more information  mathias seidel &amp; sossy hamouche</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>74</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>we are pleased to welcome first abu dhabi bank (fab) as part of our growing network. • we are very pleased to give a warm welcome to a new ahk member. • for more information mathias seidel &amp; sossy hamouche</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>3. First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ali Mohamed Haji AlKhoori</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46126.41715539352</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>It was a pleasure meeting with Kayed Ali Khorma, Group CEO of Emirates Stallions Group, and Dr.Yazan Aljabery, Consultant Surgeon at Cleveland Clinic Abu Dhabi, alongside AKRAM EZZEDDINE MAKAREM, Global Head of Family Groups &amp; Conglomerates at First Abu Dhabi Bank (FAB).</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>74</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ali-mohamed-haji-alkhoori-b3868010b_it-was-a-pleasure-meeting-with-kayed-ali-activity-7449698127214845953-MhLg?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAnqdHEBFhqGaTrppCJUDaUVNvGCvqYCUps</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449698127214845953</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>FAB</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>it was a pleasure meeting with kayed ali khorma, group ceo of emirates stallions group, and dr.yazan aljabery, consultant surgeon at cleveland clinic abu dhabi, alongside akram ezzeddine makarem, global head of family groups &amp; conglomerates at first abu dhabi bank (fab).</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Ali Mohamed Haji AlKhoori</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>it was a pleasure meeting with kayed ali khorma, group ceo of emirates stallions group, and dr.yazan aljabery, consultant surgeon at cleveland clinic abu dhabi, alongside akram ezzeddine makarem, global head of family groups &amp; conglomerates at first abu dhabi bank (fab).</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>75</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>it was a pleasure meeting with kayed ali khorma, group ceo of emirates stallions group, and dr.yazan aljabery, consultan…</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>3. First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Manikandan Sundaram PMP PSM CSPO</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46126.25002107639</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>🗞️ GCC Banking Tech Roundup — Edition #275 | 14 Apr 2026
+Your crisp daily roundup of top banking-tech developments across the GCC — focused on innovation, AI, and financial transformation.
+🔹 UAE – First Abu Dhabi Bank (FAB): Advances its AI-driven trade finance platform to digitize document processing and automate risk checks.
+💡 Impact: Speeds up transaction cycles while improving accuracy in trade operations.
+🔹 KSA – alrajhi bank: Expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions.
+💡 Impact: Strengthens payment efficiency and supports growing digital transaction volumes.
+🔹 Qatar – Commercial Bank: Introduces AI-powered customer insights engine to personalize product offerings across digital channels.
+💡 Impact: Drives targeted engagement and improves cross-sell effectiveness.
+🔹 Bahrain – Bank ABC: Enhances its cross-border payments platform using blockchain-based settlement capabilities.
+💡 Impact: Reduces transfer time and increases transparency in international transactions.
+🔹 Oman – Oman Arab Bank: Deploys advanced analytics for credit scoring to improve SME lending decision frameworks.
+💡 Impact: Expands access to finance while strengthening risk management.
+🔹 Kuwait – Boubyan Bank: Launches AI-enabled chatbot for Islamic banking advisory and customer support.
+💡 Impact: Improves service accessibility while scaling Sharia-compliant engagement.
+💡 Big Picture: AI-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the GCC’s shift toward faster, smarter, and more transparent banking ecosystems.
+🔁 Stay informed. Share this update with your GCC banking and fintech network.
+#GCCBanking #AIBanking #DigitalTransformation #FintechGCC #SmartBanking #DataDrivenFinance</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/manikandansundarampmp_gccbanking-aibanking-digitaltransformation-activity-7449637559766536193-6g6a?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAnqdHEBFhqGaTrppCJUDaUVNvGCvqYCUps</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449637559766536193</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>FAB</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>gcc banking tech roundup — edition #275 | 14 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. uae – first abu dhabi bank (fab): advances its ai-driven trade finance platform to digitize document processing and automate risk checks. impact: speeds up transaction cycles while improving accuracy in trade operations. ksa – alrajhi bank: expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions. impact: strengthens payment efficiency and supports growing digital transaction volumes. qatar – commercial bank: introduces ai-powered customer insights engine to personalize product offerings across digital channels. impact: drives targeted engagement and improves cross-sell effectiveness. bahrain – bank abc: enhances its cross-border payments platform using blockchain-based settlement capabilities. impact: reduces transfer time and increases transparency in international transactions. oman – oman arab bank: deploys advanced analytics for credit scoring to improve sme lending decision frameworks. impact: expands access to finance while strengthening risk management. kuwait – boubyan bank: launches ai-enabled chatbot for islamic banking advisory and customer support. impact: improves service accessibility while scaling sharia-compliant engagement. big picture: ai-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the gcc’s shift toward faster, smarter, and more transparent banking ecosystems. stay informed. share this update with your gcc banking and fintech network. #gccbanking #aibanking #digitaltransformation #fintechgcc #smartbanking #datadrivenfinance</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Manikandan Sundaram PMP PSM CSPO</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>gcc banking tech roundup — edition #275 | 14 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. uae – first abu dhabi bank (fab): advances its ai-driven trade finance platform to digitize document processing and automate risk checks. impact: speeds up transaction cycles while improving accuracy in trade operations. ksa – alrajhi bank: expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions. impact: strengthens payment efficiency and supports growing digital transaction volumes. qatar – commercial bank: introduces ai-powered customer insights engine to personalize product offerings across digital channels. impact: drives targeted engagement and improves cross-sell effectiveness. bahrain – bank abc: enhances its cross-border payments platform using blockchain-based settlement capabilities. impact: reduces transfer time and increases transparency in international transactions. oman – oman arab bank: deploys advanced analytics for credit scoring to improve sme lending decision frameworks. impact: expands access to finance while strengthening risk management. kuwait – boubyan bank: launches ai-enabled chatbot for islamic banking advisory and customer support. impact: improves service accessibility while scaling sharia-compliant engagement. big picture: ai-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the gcc’s shift toward faster, smarter, and more transparent banking ecosystems. stay informed. share this update with your gcc banking and fintech network. #gccbanking #aibanking #digitaltransformation #fintechgcc #smartbanking #datadrivenfinance</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>76</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>gcc banking tech roundup — edition #275 | 14 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. • big picture: ai-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the gcc’s shift toward faster, smarter, and more transparent banking ecosystems. • ksa – alrajhi bank: expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions.</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>3. First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Haruna Isa Yaro</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46125.97743001158</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nigeria’s National Assembly has approved the 2026 Appropriation Bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal.
+Key figures:
+• Capital Expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports.
+• Debt Servicing: ₦15.81 trillion
+• Projected Revenue: ₦36.87 trillion
+• Fiscal Deficit: ₦31.46 trillion, partly financed by $6 billion in new external loans ($5B from First Abu Dhabi Bank and $1B from Citi Bank).
+The budget targets 4.1–4.68% GDP growth, emphasizing development. However, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders.
+What are your views on the fiscal strategy and potential economic impact?
+#NigeriaEconomy #Budget2026 #InfrastructureDevelopment #FiscalPolicy</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>linkedinVideo</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/haruna-isa-yaro-1a826a211_nigeriaeconomy-budget2026-infrastructuredevelopment-activity-7449538776072306689-acgk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAnqdHEBFhqGaTrppCJUDaUVNvGCvqYCUps</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449538776072306689</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>FAB</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>nigeria’s national assembly has approved the 2026 appropriation bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal. key figures: • capital expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports. • debt servicing: ₦15.81 trillion • projected revenue: ₦36.87 trillion • fiscal deficit: ₦31.46 trillion, partly financed by $6 billion in new external loans ($5b from first abu dhabi bank and $1b from citi bank). the budget targets 4.1–4.68% gdp growth, emphasizing development. however, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders. what are your views on the fiscal strategy and potential economic impact? #nigeriaeconomy #budget2026 #infrastructuredevelopment #fiscalpolicy</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Haruna Isa Yaro</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>nigeria’s national assembly has approved the 2026 appropriation bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal. key figures: • capital expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports. • debt servicing: ₦15.81 trillion • projected revenue: ₦36.87 trillion • fiscal deficit: ₦31.46 trillion, partly financed by $6 billion in new external loans ($5b from first abu dhabi bank and $1b from citi bank). the budget targets 4.1–4.68% gdp growth, emphasizing development. however, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders. what are your views on the fiscal strategy and potential economic impact? #nigeriaeconomy #budget2026 #infrastructuredevelopment #fiscalpolicy</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>77</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>nigeria’s national assembly has approved the 2026 appropriation bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal. • key figures: • capital expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports. • however, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders.</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>3. First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mahmoud Youssif El-Afifi</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46125.95206465277</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank Misr (FABMISR) 
+FABian and forever proud ✌️👌🌟</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mahmoud-youssif-el-afifi-04335ab4_first-abu-dhabi-bank-misr-fabmisr-fabian-activity-7449529583973900289-HyjP?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAAnqdHEBFhqGaTrppCJUDaUVNvGCvqYCUps</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>urn:li:activity:7449529583973900289</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>FAB</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>first abu dhabi bank misr (fabmisr) fabian and forever proud</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Mahmoud Youssif El-Afifi</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>first abu dhabi bank misr (fabmisr) fabian and forever proud</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>78</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>first abu dhabi bank misr (fabmisr) fabian and forever proud</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>13-04-2026</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>3. First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>First Abu Dhabi Bank (FAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>Hamdan Alyammahi</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C80" s="2" t="n">
         <v>46125.9505643287</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>🚀 Stop Treating AI as an R&amp;D Project. It’s a Structural Strategy.
 In the global race for AI supremacy, "Investing in R&amp;D" is no longer a differentiator—it’s the baseline. The real winners aren't just building models; they are choosing a Structural Blueprint to ensure their legacy doesn’t become their liability.
@@ -9038,108 +9710,108 @@
 #AIStrategy #DigitalTransformation #UAEBusiness #Leadership #FutureOfWork #StrategicThinking #Innovation</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E80" t="n">
         <v>2</v>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/hamdanalyammahi_aistrategy-digitaltransformation-uaebusiness-activity-7449529040274894848-EGhd?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACa6SM4BOEYYJg0wEbtEW0fBaNusd_6tSlw</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/hamdanalyammahi_aistrategy-digitaltransformation-uaebusiness-activity-7449529040274894848-EGhd?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEgJJw8BefmW2ngPsTOBI09zfDAq2oK3oSU</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>urn:li:activity:7449529040274894848</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>stop treating ai as an r&amp;d project. it’s a structural strategy. in the global race for ai supremacy, "investing in r&amp;d" is no longer a differentiator—it’s the baseline. the real winners aren't just building models; they are choosing a structural blueprint to ensure their legacy doesn’t become their liability. in the uae’s rapidly evolving ecosystem, we see three clear paths to avoiding "innovation stagnation." 1⃣ the brownfield "modernization" (internal evolution) the strategy: layering agentic ai directly into existing legacy cores to automate complex workflows. the synergy: turns "dormant" historical data into active intelligence. first abu dhabi bank (fab) has moved from pilots to enterprise-scale deployment, integrating over 30 agentic ai use cases across payments, compliance, and engineering. the outcome: massive gains in operational resilience. for instance, fab reduced specific client onboarding times from seven days to just one, an 88% increase in efficiency. 2⃣ the greenfield "parallel path" (the disruptor spin-off) the strategy: launching a completely new, ai-first entity that operates without legacy baggage. the synergy: look at wio bank. by creating a digital-native platform, the parent captures high-growth segments like smes and gen-z. wio recently reported a 55% revenue jump for fy2025, reaching aed 1.24 billion. the outcome: risk segregation. you can iterate in the "greenfield" without vibrating the "brownfield" core that generates steady, passive revenue. wio achieved profitability in its first year by prioritizing customer net promoter scores (nps) over traditional rigid banking structures. 3⃣ the vertical "tech-integration" (the value chain play) the strategy: building or acquiring a dedicated ai-tech arm to control your own innovation supply chain. the synergy: aiq (adnoc + g42) is the gold standard. instead of buying "off-the-shelf" ai, they built a factory. aiq recently announced a $340 million contract for large-scale agentic ai deployment across adnoc operations. the outcome: ecosystem dominance. you own the ip and the roadmap. aiq’s tools like "robowell" remotely operate equipment to reduce costs and increase production, while their "energyai" program targets 90% accuracy in production forecasts. the takeaway: ai isn't a "plug-and-play" tool; it’s a structural choice. if you try to do everything inside your legacy core, you move too slowly. if you only do it outside, you lose the power of your scale. the most successful firms are playing a hybrid game: modernizing the old while launching the new. which path is your organization taking? brownfield (revamping the engine while flying) greenfield (building the next-gen fleet in parallel) vertical (owning the factory that builds the tech) #aistrategy #digitaltransformation #uaebusiness #leadership #futureofwork #strategicthinking #innovation</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>Hamdan Alyammahi</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>stop treating ai as an r&amp;d project. it’s a structural strategy. in the global race for ai supremacy, "investing in r&amp;d" is no longer a differentiator—it’s the baseline. the real winners aren't just building models; they are choosing a structural blueprint to ensure their legacy doesn’t become their liability. in the uae’s rapidly evolving ecosystem, we see three clear paths to avoiding "innovation stagnation." 1⃣ the brownfield "modernization" (internal evolution) the strategy: layering agentic ai directly into existing legacy cores to automate complex workflows. the synergy: turns "dormant" historical data into active intelligence. first abu dhabi bank (fab) has moved from pilots to enterprise-scale deployment, integrating over 30 agentic ai use cases across payments, compliance, and engineering. the outcome: massive gains in operational resilience. for instance, fab reduced specific client onboarding times from seven days to just one, an 88% increase in efficiency. 2⃣ the greenfield "parallel path" (the disruptor spin-off) the strategy: launching a completely new, ai-first entity that operates without legacy baggage. the synergy: look at wio bank. by creating a digital-native platform, the parent captures high-growth segments like smes and gen-z. wio recently reported a 55% revenue jump for fy2025, reaching aed 1.24 billion. the outcome: risk segregation. you can iterate in the "greenfield" without vibrating the "brownfield" core that generates steady, passive revenue. wio achieved profitability in its first year by prioritizing customer net promoter scores (nps) over traditional rigid banking structures. 3⃣ the vertical "tech-integration" (the value chain play) the strategy: building or acquiring a dedicated ai-tech arm to control your own innovation supply chain. the synergy: aiq (adnoc + g42) is the gold standard. instead of buying "off-the-shelf" ai, they built a factory. aiq recently announced a $340 million contract for large-scale agentic ai deployment across adnoc operations. the outcome: ecosystem dominance. you own the ip and the roadmap. aiq’s tools like "robowell" remotely operate equipment to reduce costs and increase production, while their "energyai" program targets 90% accuracy in production forecasts. the takeaway: ai isn't a "plug-and-play" tool; it’s a structural choice. if you try to do everything inside your legacy core, you move too slowly. if you only do it outside, you lose the power of your scale. the most successful firms are playing a hybrid game: modernizing the old while launching the new. which path is your organization taking? brownfield (revamping the engine while flying) greenfield (building the next-gen fleet in parallel) vertical (owning the factory that builds the tech) #aistrategy #digitaltransformation #uaebusiness #leadership #futureofwork #strategicthinking #innovation</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R74" t="n">
-        <v>73</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>AI is a structural strategy, not just an R&amp;D project. • First Abu Dhabi Bank reduced client onboarding from seven days to one, achieving 88% efficiency. • Wio Bank reported a 55% revenue increase for FY2025, reaching AED 1.24 billion.</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
+      <c r="R80" t="n">
+        <v>79</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>2⃣ the greenfield "parallel path" (the disruptor spin-off) the strategy: launching a completely new, ai-first entity that operates without legacy baggage. • first abu dhabi bank (fab) has moved from pilots to enterprise-scale deployment, integrating over 30 agentic ai use cases across payments, compliance, and engineering. • wio recently reported a 55% revenue jump for fy2025, reaching aed 1.24 billion.</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B75" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>Mohamed Abdel-Salam</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C81" s="2" t="n">
         <v>46125.82369238426</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>As a Mechanical Technical Office Engineer, I had the opportunity to work on First Abu Dhabi Bank (FAB)- Maadi Laselky St. Branch.
 My key responsibilities included:
@@ -9152,108 +9824,108 @@
 #MEP #MechanicalEngineering #TechnicalOffice #ShopDrawings #AsBuilt #FAB #HVAC #FireFighting</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>7</v>
-      </c>
-      <c r="F75" t="n">
+      <c r="E81" t="n">
+        <v>8</v>
+      </c>
+      <c r="F81" t="n">
         <v>2</v>
       </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/mohamed-abdel-salam-5ab206277_mep-mechanicalengineering-technicaloffice-activity-7449483063421714432-Iv9P?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACa6SM4BOEYYJg0wEbtEW0fBaNusd_6tSlw</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mohamed-abdel-salam-5ab206277_mep-mechanicalengineering-technicaloffice-activity-7449483063421714432-Iv9P?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEgJJw8BefmW2ngPsTOBI09zfDAq2oK3oSU</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>urn:li:activity:7449483063421714432</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>as a mechanical technical office engineer, i had the opportunity to work on first abu dhabi bank (fab)- maadi laselky st. branch. my key responsibilities included: -preparing shop drawings fully coordinated and approved by the consultant. -submitting &amp; following up on material submittals. -performing quantity surveying and accurate take-offs. -delivering as-built drawings reflecting final site conditions. close coordination with the architectural and electrical teams was essential to avoid clashes and ensure full system integration. grateful to my project team for the great collaboration! #mep #mechanicalengineering #technicaloffice #shopdrawings #asbuilt #fab #hvac #firefighting</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Mohamed Abdel-Salam</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>as a mechanical technical office engineer, i had the opportunity to work on first abu dhabi bank (fab)- maadi laselky st. branch. my key responsibilities included: -preparing shop drawings fully coordinated and approved by the consultant. -submitting &amp; following up on material submittals. -performing quantity surveying and accurate take-offs. -delivering as-built drawings reflecting final site conditions. close coordination with the architectural and electrical teams was essential to avoid clashes and ensure full system integration. grateful to my project team for the great collaboration! #mep #mechanicalengineering #technicaloffice #shopdrawings #asbuilt #fab #hvac #firefighting</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="R75" t="n">
-        <v>74</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Worked on First Abu Dhabi Bank (FAB) Maadi Laselky St. branch project. • Prepared coordinated shop drawings and submitted material submittals. • Delivered as-built drawings and performed quantity surveying.</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
+      <c r="R81" t="n">
+        <v>80</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>as a mechanical technical office engineer, i had the opportunity to work on first abu dhabi bank (fab)- maadi laselky st. • close coordination with the architectural and electrical teams was essential to avoid clashes and ensure full system integration. • my key responsibilities included: -preparing shop drawings fully coordinated and approved by the consultant.</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B76" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>Dr. Souhayel Tayeb</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C82" s="2" t="n">
         <v>46125.79888634259</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>The New Architecture of African Sovereign Debt: between domestic pivots, derivative traps, and the missing balance sheet.
 Three concurrent forces are reshaping African sovereign finance and the international financial architecture is not keeping pace.
@@ -9267,108 +9939,108 @@
 #SovereignDebt #Africa #TotalReturnSwaps #DomesticDebt #DebtRestructuring #IMF #UNCTAD #CapitalMarkets #Nigeria #Angola #Senegal #PublicFinance #FinancialStability #CommonFramework #DIFC #GCC</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>3</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>article</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/dr-souhayel-tayeb-855989313_sovereigndebt-africa-totalreturnswaps-activity-7449474074013253633-Fe_y?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACa6SM4BOEYYJg0wEbtEW0fBaNusd_6tSlw</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/dr-souhayel-tayeb-855989313_sovereigndebt-africa-totalreturnswaps-activity-7449474074013253633-Fe_y?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEgJJw8BefmW2ngPsTOBI09zfDAq2oK3oSU</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>urn:li:activity:7449474074013253633</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>FAB</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>the new architecture of african sovereign debt: between domestic pivots, derivative traps, and the missing balance sheet. three concurrent forces are reshaping african sovereign finance and the international financial architecture is not keeping pace. first, sub-saharan african governments have pivoted decisively from external to domestic borrowing. as amadou sy and athene laws document in their excellent international monetary fund finance &amp; development analysis (march 2026), most of the region's public debt is now domestic. the benefits are real: reduced currency mismatch, stronger local capital markets, greater monetary policy autonomy. so are the risks: a median issuance rate of 8.8%, maturities measured in months rather than decades, and a sovereign-bank nexus growing faster in africa than anywhere else in the world. second, a wave of total return swaps has emerged as sovereign financing tools, never designed for this purpose. nigeria (usd 5 billion with first abu dhabi bank (fab)), angola (usd 2.5 billion with j.p. morgan and africa finance corporation), and senegal (eur 650 million to usd 1.3 billion across seven transactions with afc, fab, and others) have collectively tapped billions through derivative structures that sit outside conventional debt covenants, distort public debt statistics, and create contingent liabilities that only fully crystallise at default. angola's usd 200 million margin call in may 2025 (triggered by falling oil prices) showed how quickly these instruments turn from cost-saving tools into fiscal emergencies. third, servicing costs continue to escalate. un trade and development (unctad) reports that developing countries paid a record usd 921 billion in net interest in 2024. sub-saharan africa now spends 18.7% of government revenue on external debt service, three times the level in 2014. today, 3.4 billion people live in countries spending more on debt servicing than on health or education. and then there is what udaibir saran das rightly calls the missing variable: what does all this borrowing actually build? when nigeria allocates 72% of spending to recurrent expenditure and 69% of revenue to debt service, the liability side compounds while the asset side remains thin. i have attempted to bring these threads together in a single analytical framework. the composition of sovereign debt matters as much as its quantum. what borrowed capital builds matters as much as what sovereigns owe. these are the missing variables in africa's debt equation. #sovereigndebt #africa #totalreturnswaps #domesticdebt #debtrestructuring #imf #unctad #capitalmarkets #nigeria #angola #senegal #publicfinance #financialstability #commonframework #difc #gcc</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Dr. Souhayel Tayeb</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>the new architecture of african sovereign debt: between domestic pivots, derivative traps, and the missing balance sheet. three concurrent forces are reshaping african sovereign finance and the international financial architecture is not keeping pace. first, sub-saharan african governments have pivoted decisively from external to domestic borrowing. as amadou sy and athene laws document in their excellent international monetary fund finance &amp; development analysis (march 2026), most of the region's public debt is now domestic. the benefits are real: reduced currency mismatch, stronger local capital markets, greater monetary policy autonomy. so are the risks: a median issuance rate of 8.8%, maturities measured in months rather than decades, and a sovereign-bank nexus growing faster in africa than anywhere else in the world. second, a wave of total return swaps has emerged as sovereign financing tools, never designed for this purpose. nigeria (usd 5 billion with first abu dhabi bank (fab)), angola (usd 2.5 billion with j.p. morgan and africa finance corporation), and senegal (eur 650 million to usd 1.3 billion across seven transactions with afc, fab, and others) have collectively tapped billions through derivative structures that sit outside conventional debt covenants, distort public debt statistics, and create contingent liabilities that only fully crystallise at default. angola's usd 200 million margin call in may 2025 (triggered by falling oil prices) showed how quickly these instruments turn from cost-saving tools into fiscal emergencies. third, servicing costs continue to escalate. un trade and development (unctad) reports that developing countries paid a record usd 921 billion in net interest in 2024. sub-saharan africa now spends 18.7% of government revenue on external debt service, three times the level in 2014. today, 3.4 billion people live in countries spending more on debt servicing than on health or education. and then there is what udaibir saran das rightly calls the missing variable: what does all this borrowing actually build? when nigeria allocates 72% of spending to recurrent expenditure and 69% of revenue to debt service, the liability side compounds while the asset side remains thin. i have attempted to bring these threads together in a single analytical framework. the composition of sovereign debt matters as much as its quantum. what borrowed capital builds matters as much as what sovereigns owe. these are the missing variables in africa's debt equation. #sovereigndebt #africa #totalreturnswaps #domesticdebt #debtrestructuring #imf #unctad #capitalmarkets #nigeria #angola #senegal #publicfinance #financialstability #commonframework #difc #gcc</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="R76" t="n">
-        <v>75</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa shifts from external to domestic borrowing, increasing risks and costs. • Total return swaps are used for sovereign financing, creating contingent liabilities. • Sub-Saharan Africa spends 18.7% of revenue on external debt service, up from 6.2% in 2014.</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
+      <c r="R82" t="n">
+        <v>81</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>sub-saharan africa now spends 18.7% of government revenue on external debt service, three times the level in 2014. • as amadou sy and athene laws document in their excellent international monetary fund finance &amp; development analysis (march 2026), most of the region's public debt is now domestic. • angola's usd 200 million margin call in may 2025 (triggered by falling oil prices) showed how quickly these instruments turn from cost-saving tools into fiscal emergencies.</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>13-04-2026</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>3. First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>First Abu Dhabi Bank (FAB)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B77" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Sara ALkhyeli</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C83" s="2" t="n">
         <v>46125.72054017361</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Grateful for new beginnings and the opportunity to grow with First Abu Dhabi Bank (FAB) .  
 I truly believe that nothing worth having is achieved without effort — you don’t earn it until you work for it, and you don’t reach it until you deserve it.  
@@ -9376,683 +10048,11 @@
 #CareerJourney #GrowthMindset #FirstAbuDhabiBank</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E83" t="n">
         <v>31</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F83" t="n">
         <v>4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/sara-alkhyeli-1740b2364_careerjourney-growthmindset-firstabudhabibank-activity-7449445682312216576-dJi0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAACa6SM4BOEYYJg0wEbtEW0fBaNusd_6tSlw</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449445682312216576</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>FAB</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>grateful for new beginnings and the opportunity to grow with first abu dhabi bank (fab) . i truly believe that nothing worth having is achieved without effort — you don’t earn it until you work for it, and you don’t reach it until you deserve it. excited for what lies ahead, ready to learn, build, and give my absolute best every step of the way. #careerjourney #growthmindset #firstabudhabibank</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Sara ALkhyeli</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>grateful for new beginnings and the opportunity to grow with first abu dhabi bank (fab) . i truly believe that nothing worth having is achieved without effort — you don’t earn it until you work for it, and you don’t reach it until you deserve it. excited for what lies ahead, ready to learn, build, and give my absolute best every step of the way. #careerjourney #growthmindset #firstabudhabibank</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="R77" t="n">
-        <v>76</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Joined First Abu Dhabi Bank (FAB) for new beginnings. • Emphasizes effort and deserving success in career. • Committed to learning and contributing fully.</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>3. First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Carla Blondel</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>46126.4631515625</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Proud moment 🤍 
-Seeing the “Together We Move Forward” campaign with First Abu Dhabi Bank (FAB) come to life out in the real world felt special. 🙏🏼
-There is something powerful about being part of a message that reflects unity and resilience. 🇦🇪 
-Even during challenging times, the UAE continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. Always moving forward. ✨</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>3</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/carla-blondel_proud-moment-seeing-the-together-we-activity-7449714795668250625-AWup?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGTWu38BIJiAvM4KvirQZm8dRyl8gnTcm84</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449714795668250625</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>FAB</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>proud moment seeing the “together we move forward” campaign with first abu dhabi bank (fab) come to life out in the real world felt special. there is something powerful about being part of a message that reflects unity and resilience. even during challenging times, the uae continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. always moving forward.</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Carla Blondel</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>proud moment seeing the “together we move forward” campaign with first abu dhabi bank (fab) come to life out in the real world felt special. there is something powerful about being part of a message that reflects unity and resilience. even during challenging times, the uae continues to show its strength through its people, its spirit, and the way it brings everyone together with a shared sense of purpose and support. always moving forward.</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="R78" t="n">
-        <v>77</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>"Together we move forward" campaign launched with First Abu Dhabi Bank (FAB). • The UAE demonstrates unity and resilience during challenging times. • The campaign reflects a shared sense of purpose and support among people.</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>14-04-2026</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>3. First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>German Emirati Joint Council for Industry &amp; Commerce (AHK)</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>46126.45378488426</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>We are very pleased to give a warm welcome to a new AHK Member.
-We are pleased to welcome First Abu Dhabi Bank (FAB) as part of our growing network.
-First Abu Dhabi Bank (FAB) is the UAE’s global bank, and one of the world’s largest and safest financial institutions, with an international network that spans five continents and a presence in 20 markets to facilitate cross-border liquidity, trade, and investment flows. With the strongest combined credit rating among any other bank in the MENA region (Aa3/AA-/AA- by Moody’s, S&amp;P, and Fitch, respectively, with a stable outlook) and total assets of AED 1.34 trillion (USD 366 billion) as of June-end 2025, FAB offers an extensive range of tailor-made products and services to meet the banking needs of our customers in the UAE and the international markets.
-For more information www.bankfab.com
-Mathias Seidel &amp; Sossy Hamouche</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>3</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/german-emirati-joint-council-for-industry-and-commerce-ahk-_we-are-very-pleased-to-give-a-warm-welcome-activity-7449711401297719296-rFcx?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGTWu38BIJiAvM4KvirQZm8dRyl8gnTcm84</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449711401297719296</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>FAB</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>we are very pleased to give a warm welcome to a new ahk member. we are pleased to welcome first abu dhabi bank (fab) as part of our growing network. first abu dhabi bank (fab) is the uae’s global bank, and one of the world’s largest and safest financial institutions, with an international network that spans five continents and a presence in 20 markets to facilitate cross-border liquidity, trade, and investment flows. with the strongest combined credit rating among any other bank in the mena region (aa3/aa-/aa- by moody’s, s&amp;p, and fitch, respectively, with a stable outlook) and total assets of aed 1.34 trillion (usd 366 billion) as of june-end 2025, fab offers an extensive range of tailor-made products and services to meet the banking needs of our customers in the uae and the international markets. for more information  mathias seidel &amp; sossy hamouche</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>German Emirati Joint Council for Industry &amp; Commerce (AHK)</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>we are very pleased to give a warm welcome to a new ahk member. we are pleased to welcome first abu dhabi bank (fab) as part of our growing network. first abu dhabi bank (fab) is the uae’s global bank, and one of the world’s largest and safest financial institutions, with an international network that spans five continents and a presence in 20 markets to facilitate cross-border liquidity, trade, and investment flows. with the strongest combined credit rating among any other bank in the mena region (aa3/aa-/aa- by moody’s, s&amp;p, and fitch, respectively, with a stable outlook) and total assets of aed 1.34 trillion (usd 366 billion) as of june-end 2025, fab offers an extensive range of tailor-made products and services to meet the banking needs of our customers in the uae and the international markets. for more information  mathias seidel &amp; sossy hamouche</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="R79" t="n">
-        <v>78</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB) joins the AHK network. • FAB has total assets of AED 1.34 trillion (USD 366 billion). • FAB holds the strongest credit rating in the MENA region.</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>14-04-2026</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>3. First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Ali Mohamed Haji AlKhoori</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>46126.41715539352</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>It was a pleasure meeting with Kayed Ali Khorma, Group CEO of Emirates Stallions Group, and Dr.Yazan Aljabery, Consultant Surgeon at Cleveland Clinic Abu Dhabi, alongside AKRAM EZZEDDINE MAKAREM, Global Head of Family Groups &amp; Conglomerates at First Abu Dhabi Bank (FAB).</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>73</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/ali-mohamed-haji-alkhoori-b3868010b_it-was-a-pleasure-meeting-with-kayed-ali-activity-7449698127214845953-MhLg?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGTWu38BIJiAvM4KvirQZm8dRyl8gnTcm84</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449698127214845953</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>FAB</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>it was a pleasure meeting with kayed ali khorma, group ceo of emirates stallions group, and dr.yazan aljabery, consultant surgeon at cleveland clinic abu dhabi, alongside akram ezzeddine makarem, global head of family groups &amp; conglomerates at first abu dhabi bank (fab).</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Ali Mohamed Haji AlKhoori</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>it was a pleasure meeting with kayed ali khorma, group ceo of emirates stallions group, and dr.yazan aljabery, consultant surgeon at cleveland clinic abu dhabi, alongside akram ezzeddine makarem, global head of family groups &amp; conglomerates at first abu dhabi bank (fab).</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R80" t="n">
-        <v>79</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Meeting included Kayed Ali Khorma, CEO of Emirates Stallions Group. • Dr. Yazan Aljabery is a consultant surgeon at Cleveland Clinic Abu Dhabi. • Akram Ezzeddine Makarem is the global head of family groups at FAB.</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>14-04-2026</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>3. First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Manikandan Sundaram PMP PSM CSPO</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>46126.25002107639</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>🗞️ GCC Banking Tech Roundup — Edition #275 | 14 Apr 2026
-Your crisp daily roundup of top banking-tech developments across the GCC — focused on innovation, AI, and financial transformation.
-🔹 UAE – First Abu Dhabi Bank (FAB): Advances its AI-driven trade finance platform to digitize document processing and automate risk checks.
-💡 Impact: Speeds up transaction cycles while improving accuracy in trade operations.
-🔹 KSA – alrajhi bank: Expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions.
-💡 Impact: Strengthens payment efficiency and supports growing digital transaction volumes.
-🔹 Qatar – Commercial Bank: Introduces AI-powered customer insights engine to personalize product offerings across digital channels.
-💡 Impact: Drives targeted engagement and improves cross-sell effectiveness.
-🔹 Bahrain – Bank ABC: Enhances its cross-border payments platform using blockchain-based settlement capabilities.
-💡 Impact: Reduces transfer time and increases transparency in international transactions.
-🔹 Oman – Oman Arab Bank: Deploys advanced analytics for credit scoring to improve SME lending decision frameworks.
-💡 Impact: Expands access to finance while strengthening risk management.
-🔹 Kuwait – Boubyan Bank: Launches AI-enabled chatbot for Islamic banking advisory and customer support.
-💡 Impact: Improves service accessibility while scaling Sharia-compliant engagement.
-💡 Big Picture: AI-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the GCC’s shift toward faster, smarter, and more transparent banking ecosystems.
-🔁 Stay informed. Share this update with your GCC banking and fintech network.
-#GCCBanking #AIBanking #DigitalTransformation #FintechGCC #SmartBanking #DataDrivenFinance</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/manikandansundarampmp_gccbanking-aibanking-digitaltransformation-activity-7449637559766536193-6g6a?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGTWu38BIJiAvM4KvirQZm8dRyl8gnTcm84</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449637559766536193</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>FAB</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>gcc banking tech roundup — edition #275 | 14 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. uae – first abu dhabi bank (fab): advances its ai-driven trade finance platform to digitize document processing and automate risk checks. impact: speeds up transaction cycles while improving accuracy in trade operations. ksa – alrajhi bank: expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions. impact: strengthens payment efficiency and supports growing digital transaction volumes. qatar – commercial bank: introduces ai-powered customer insights engine to personalize product offerings across digital channels. impact: drives targeted engagement and improves cross-sell effectiveness. bahrain – bank abc: enhances its cross-border payments platform using blockchain-based settlement capabilities. impact: reduces transfer time and increases transparency in international transactions. oman – oman arab bank: deploys advanced analytics for credit scoring to improve sme lending decision frameworks. impact: expands access to finance while strengthening risk management. kuwait – boubyan bank: launches ai-enabled chatbot for islamic banking advisory and customer support. impact: improves service accessibility while scaling sharia-compliant engagement. big picture: ai-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the gcc’s shift toward faster, smarter, and more transparent banking ecosystems. stay informed. share this update with your gcc banking and fintech network. #gccbanking #aibanking #digitaltransformation #fintechgcc #smartbanking #datadrivenfinance</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Manikandan Sundaram PMP PSM CSPO</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>gcc banking tech roundup — edition #275 | 14 apr 2026 your crisp daily roundup of top banking-tech developments across the gcc — focused on innovation, ai, and financial transformation. uae – first abu dhabi bank (fab): advances its ai-driven trade finance platform to digitize document processing and automate risk checks. impact: speeds up transaction cycles while improving accuracy in trade operations. ksa – alrajhi bank: expands its digital payments infrastructure with enhanced real-time processing capabilities for retail transactions. impact: strengthens payment efficiency and supports growing digital transaction volumes. qatar – commercial bank: introduces ai-powered customer insights engine to personalize product offerings across digital channels. impact: drives targeted engagement and improves cross-sell effectiveness. bahrain – bank abc: enhances its cross-border payments platform using blockchain-based settlement capabilities. impact: reduces transfer time and increases transparency in international transactions. oman – oman arab bank: deploys advanced analytics for credit scoring to improve sme lending decision frameworks. impact: expands access to finance while strengthening risk management. kuwait – boubyan bank: launches ai-enabled chatbot for islamic banking advisory and customer support. impact: improves service accessibility while scaling sharia-compliant engagement. big picture: ai-led automation, real-time payments, and blockchain-backed infrastructure are accelerating the gcc’s shift toward faster, smarter, and more transparent banking ecosystems. stay informed. share this update with your gcc banking and fintech network. #gccbanking #aibanking #digitaltransformation #fintechgcc #smartbanking #datadrivenfinance</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R81" t="n">
-        <v>80</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>FAB advances AI-driven trade finance platform for faster, more accurate transactions. • Alrajhi Bank enhances digital payments with real-time processing for retail transactions. • Bank ABC improves cross-border payments using blockchain for faster, transparent transactions.</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>14-04-2026</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>3. First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Haruna Isa Yaro</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>46125.97743001158</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Nigeria’s National Assembly has approved the 2026 Appropriation Bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal.
-Key figures:
-• Capital Expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports.
-• Debt Servicing: ₦15.81 trillion
-• Projected Revenue: ₦36.87 trillion
-• Fiscal Deficit: ₦31.46 trillion, partly financed by $6 billion in new external loans ($5B from First Abu Dhabi Bank and $1B from Citi Bank).
-The budget targets 4.1–4.68% GDP growth, emphasizing development. However, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders.
-What are your views on the fiscal strategy and potential economic impact?
-#NigeriaEconomy #Budget2026 #InfrastructureDevelopment #FiscalPolicy</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>linkedinVideo</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/haruna-isa-yaro-1a826a211_nigeriaeconomy-budget2026-infrastructuredevelopment-activity-7449538776072306689-acgk?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGTWu38BIJiAvM4KvirQZm8dRyl8gnTcm84</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>urn:li:activity:7449538776072306689</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>FAB</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>nigeria’s national assembly has approved the 2026 appropriation bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal. key figures: • capital expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports. • debt servicing: ₦15.81 trillion • projected revenue: ₦36.87 trillion • fiscal deficit: ₦31.46 trillion, partly financed by $6 billion in new external loans ($5b from first abu dhabi bank and $1b from citi bank). the budget targets 4.1–4.68% gdp growth, emphasizing development. however, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders. what are your views on the fiscal strategy and potential economic impact? #nigeriaeconomy #budget2026 #infrastructuredevelopment #fiscalpolicy</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Haruna Isa Yaro</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>nigeria’s national assembly has approved the 2026 appropriation bill at ₦68.32 trillion, a significant increase from the initial ₦58.47 trillion proposal. key figures: • capital expenditure: ₦32.29 trillion (47%) – focused on critical infrastructure including roads, railways, power, and ports. • debt servicing: ₦15.81 trillion • projected revenue: ₦36.87 trillion • fiscal deficit: ₦31.46 trillion, partly financed by $6 billion in new external loans ($5b from first abu dhabi bank and $1b from citi bank). the budget targets 4.1–4.68% gdp growth, emphasizing development. however, concerns around debt sustainability, high debt servicing costs, and implementation effectiveness remain critical for stakeholders. what are your views on the fiscal strategy and potential economic impact? #nigeriaeconomy #budget2026 #infrastructuredevelopment #fiscalpolicy</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="R82" t="n">
-        <v>81</v>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Nigeria's 2026 appropriation bill approved at ₦68.32 trillion, up from ₦58.47 trillion. • Capital expenditure allocated ₦32.29 trillion for infrastructure projects. • Fiscal deficit projected at ₦31.46 trillion, partly financed by $6 billion in new loans.</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>13-04-2026</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>3. First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank (FAB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Mahmoud Youssif El-Afifi</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>46125.95206465277</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>First Abu Dhabi Bank Misr (FABMISR) 
-FABian and forever proud ✌️👌🌟</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>4</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -10065,12 +10065,12 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/posts/mahmoud-youssif-el-afifi-04335ab4_first-abu-dhabi-bank-misr-fabmisr-fabian-activity-7449529583973900289-HyjP?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAGTWu38BIJiAvM4KvirQZm8dRyl8gnTcm84</t>
+          <t>https://www.linkedin.com/posts/sara-alkhyeli-1740b2364_careerjourney-growthmindset-firstabudhabibank-activity-7449445682312216576-dJi0?utm_source=combined_share_message&amp;utm_medium=member_desktop&amp;rcm=ACoAAEgJJw8BefmW2ngPsTOBI09zfDAq2oK3oSU</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>urn:li:activity:7449529583973900289</t>
+          <t>urn:li:activity:7449445682312216576</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>first abu dhabi bank misr (fabmisr) fabian and forever proud</t>
+          <t>grateful for new beginnings and the opportunity to grow with first abu dhabi bank (fab) . i truly believe that nothing worth having is achieved without effort — you don’t earn it until you work for it, and you don’t reach it until you deserve it. excited for what lies ahead, ready to learn, build, and give my absolute best every step of the way. #careerjourney #growthmindset #firstabudhabibank</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Mahmoud Youssif El-Afifi</t>
+          <t>Sara ALkhyeli</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>first abu dhabi bank misr (fabmisr) fabian and forever proud</t>
+          <t>grateful for new beginnings and the opportunity to grow with first abu dhabi bank (fab) . i truly believe that nothing worth having is achieved without effort — you don’t earn it until you work for it, and you don’t reach it until you deserve it. excited for what lies ahead, ready to learn, build, and give my absolute best every step of the way. #careerjourney #growthmindset #firstabudhabibank</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank Misr (FABMisr) is a key financial institution. • The bank emphasizes pride in its heritage and achievements. • "Fabian" likely refers to a brand or initiative associated with FABMisr.</t>
+          <t>i truly believe that nothing worth having is achieved without effort — you don’t earn it until you work for it, and you don’t reach it until you deserve it. • excited for what lies ahead, ready to learn, build, and give my absolute best every step of the way. • grateful for new beginnings and the opportunity to grow with first abu dhabi bank (fab) .</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
